--- a/artfynd/A 37730-2023 artfynd.xlsx
+++ b/artfynd/A 37730-2023 artfynd.xlsx
@@ -1750,10 +1750,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128601862</v>
+        <v>128601881</v>
       </c>
       <c r="B13" t="n">
-        <v>57682</v>
+        <v>79083</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1761,42 +1761,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>446307</v>
+        <v>446035</v>
       </c>
       <c r="R13" t="n">
-        <v>6820425</v>
+        <v>6820374</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1855,7 +1847,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128601881</v>
+        <v>128601914</v>
       </c>
       <c r="B14" t="n">
         <v>79083</v>
@@ -1890,10 +1882,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>446035</v>
+        <v>446152</v>
       </c>
       <c r="R14" t="n">
-        <v>6820374</v>
+        <v>6820406</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1952,45 +1944,53 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128601870</v>
+        <v>128601862</v>
       </c>
       <c r="B15" t="n">
-        <v>97448</v>
+        <v>57682</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>446224</v>
+        <v>446307</v>
       </c>
       <c r="R15" t="n">
-        <v>6820433</v>
+        <v>6820425</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2049,32 +2049,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128601914</v>
+        <v>128601870</v>
       </c>
       <c r="B16" t="n">
-        <v>79083</v>
+        <v>97448</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2084,10 +2084,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>446152</v>
+        <v>446224</v>
       </c>
       <c r="R16" t="n">
-        <v>6820406</v>
+        <v>6820433</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2344,10 +2344,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128601864</v>
+        <v>128601909</v>
       </c>
       <c r="B19" t="n">
-        <v>57682</v>
+        <v>79083</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2355,21 +2355,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2379,10 +2379,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>446223</v>
+        <v>446185</v>
       </c>
       <c r="R19" t="n">
-        <v>6820431</v>
+        <v>6820420</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2441,10 +2441,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128601909</v>
+        <v>128601864</v>
       </c>
       <c r="B20" t="n">
-        <v>79083</v>
+        <v>57682</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2452,21 +2452,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2476,10 +2476,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>446185</v>
+        <v>446223</v>
       </c>
       <c r="R20" t="n">
-        <v>6820420</v>
+        <v>6820431</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2635,32 +2635,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128601869</v>
+        <v>128601911</v>
       </c>
       <c r="B22" t="n">
-        <v>97448</v>
+        <v>79083</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2670,10 +2670,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>446357</v>
+        <v>446097</v>
       </c>
       <c r="R22" t="n">
-        <v>6820512</v>
+        <v>6820410</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2732,7 +2732,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128601911</v>
+        <v>128601918</v>
       </c>
       <c r="B23" t="n">
         <v>79083</v>
@@ -2767,10 +2767,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>446097</v>
+        <v>446114</v>
       </c>
       <c r="R23" t="n">
-        <v>6820410</v>
+        <v>6820373</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2829,32 +2829,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128601918</v>
+        <v>128601869</v>
       </c>
       <c r="B24" t="n">
-        <v>79083</v>
+        <v>97448</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2864,10 +2864,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>446114</v>
+        <v>446357</v>
       </c>
       <c r="R24" t="n">
-        <v>6820373</v>
+        <v>6820512</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 37730-2023 artfynd.xlsx
+++ b/artfynd/A 37730-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128601913</v>
       </c>
       <c r="B2" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128601912</v>
       </c>
       <c r="B3" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128601906</v>
       </c>
       <c r="B4" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128601904</v>
       </c>
       <c r="B5" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128601916</v>
       </c>
       <c r="B6" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128601907</v>
       </c>
       <c r="B7" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128601908</v>
       </c>
       <c r="B8" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128601897</v>
       </c>
       <c r="B9" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>128601865</v>
       </c>
       <c r="B10" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>128601915</v>
       </c>
       <c r="B11" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>128601880</v>
       </c>
       <c r="B12" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>128601881</v>
       </c>
       <c r="B13" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>128601914</v>
       </c>
       <c r="B14" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>128601862</v>
       </c>
       <c r="B15" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         <v>128601870</v>
       </c>
       <c r="B16" t="n">
-        <v>97448</v>
+        <v>97454</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>128601921</v>
       </c>
       <c r="B17" t="n">
-        <v>90954</v>
+        <v>90960</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>128601919</v>
       </c>
       <c r="B18" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2344,10 +2344,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128601909</v>
+        <v>128601864</v>
       </c>
       <c r="B19" t="n">
-        <v>79083</v>
+        <v>57686</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2355,21 +2355,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2379,10 +2379,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>446185</v>
+        <v>446223</v>
       </c>
       <c r="R19" t="n">
-        <v>6820420</v>
+        <v>6820431</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2441,10 +2441,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128601864</v>
+        <v>128601909</v>
       </c>
       <c r="B20" t="n">
-        <v>57682</v>
+        <v>79087</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2452,21 +2452,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2476,10 +2476,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>446223</v>
+        <v>446185</v>
       </c>
       <c r="R20" t="n">
-        <v>6820431</v>
+        <v>6820420</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2541,7 +2541,7 @@
         <v>128601873</v>
       </c>
       <c r="B21" t="n">
-        <v>78841</v>
+        <v>78845</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>128601911</v>
       </c>
       <c r="B22" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
         <v>128601918</v>
       </c>
       <c r="B23" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>128601869</v>
       </c>
       <c r="B24" t="n">
-        <v>97448</v>
+        <v>97454</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2926,10 +2926,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128601882</v>
+        <v>128601863</v>
       </c>
       <c r="B25" t="n">
-        <v>79083</v>
+        <v>57686</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2937,34 +2937,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>446143</v>
+        <v>446183</v>
       </c>
       <c r="R25" t="n">
-        <v>6820358</v>
+        <v>6820440</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3023,10 +3031,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128601876</v>
+        <v>128601882</v>
       </c>
       <c r="B26" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3058,10 +3066,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>446231</v>
+        <v>446143</v>
       </c>
       <c r="R26" t="n">
-        <v>6820457</v>
+        <v>6820358</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3120,10 +3128,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128601863</v>
+        <v>128601876</v>
       </c>
       <c r="B27" t="n">
-        <v>57682</v>
+        <v>79087</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3131,42 +3139,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>446183</v>
+        <v>446231</v>
       </c>
       <c r="R27" t="n">
-        <v>6820440</v>
+        <v>6820457</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3228,7 +3228,7 @@
         <v>128601866</v>
       </c>
       <c r="B28" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>128601871</v>
       </c>
       <c r="B29" t="n">
-        <v>97448</v>
+        <v>97454</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>128601917</v>
       </c>
       <c r="B30" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>128601903</v>
       </c>
       <c r="B31" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3624,7 +3624,7 @@
         <v>128601900</v>
       </c>
       <c r="B32" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3721,7 +3721,7 @@
         <v>128601905</v>
       </c>
       <c r="B33" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3818,7 +3818,7 @@
         <v>128601902</v>
       </c>
       <c r="B34" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3915,7 +3915,7 @@
         <v>128601899</v>
       </c>
       <c r="B35" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4012,7 +4012,7 @@
         <v>128601877</v>
       </c>
       <c r="B36" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4109,7 +4109,7 @@
         <v>128601879</v>
       </c>
       <c r="B37" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
         <v>128601910</v>
       </c>
       <c r="B38" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 37730-2023 artfynd.xlsx
+++ b/artfynd/A 37730-2023 artfynd.xlsx
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128601897</v>
+        <v>128601865</v>
       </c>
       <c r="B9" t="n">
-        <v>79087</v>
+        <v>57686</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,34 +1365,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>446488</v>
+        <v>446361</v>
       </c>
       <c r="R9" t="n">
-        <v>6820524</v>
+        <v>6820513</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,10 +1459,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128601865</v>
+        <v>128601897</v>
       </c>
       <c r="B10" t="n">
-        <v>57686</v>
+        <v>79087</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,42 +1470,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>446361</v>
+        <v>446488</v>
       </c>
       <c r="R10" t="n">
-        <v>6820513</v>
+        <v>6820524</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -2052,7 +2052,7 @@
         <v>128601870</v>
       </c>
       <c r="B16" t="n">
-        <v>97454</v>
+        <v>97460</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>128601921</v>
       </c>
       <c r="B17" t="n">
-        <v>90960</v>
+        <v>90966</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>128601869</v>
       </c>
       <c r="B24" t="n">
-        <v>97454</v>
+        <v>97460</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>128601871</v>
       </c>
       <c r="B29" t="n">
-        <v>97454</v>
+        <v>97460</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 37730-2023 artfynd.xlsx
+++ b/artfynd/A 37730-2023 artfynd.xlsx
@@ -1750,10 +1750,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128601881</v>
+        <v>128601862</v>
       </c>
       <c r="B13" t="n">
-        <v>79087</v>
+        <v>57686</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1761,34 +1761,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>446035</v>
+        <v>446307</v>
       </c>
       <c r="R13" t="n">
-        <v>6820374</v>
+        <v>6820425</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1847,32 +1855,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128601914</v>
+        <v>128601870</v>
       </c>
       <c r="B14" t="n">
-        <v>79087</v>
+        <v>97460</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1882,10 +1890,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>446152</v>
+        <v>446224</v>
       </c>
       <c r="R14" t="n">
-        <v>6820406</v>
+        <v>6820433</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1944,10 +1952,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128601862</v>
+        <v>128601881</v>
       </c>
       <c r="B15" t="n">
-        <v>57686</v>
+        <v>79087</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1955,42 +1963,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>446307</v>
+        <v>446035</v>
       </c>
       <c r="R15" t="n">
-        <v>6820425</v>
+        <v>6820374</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2049,32 +2049,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128601870</v>
+        <v>128601914</v>
       </c>
       <c r="B16" t="n">
-        <v>97460</v>
+        <v>79087</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2084,10 +2084,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>446224</v>
+        <v>446152</v>
       </c>
       <c r="R16" t="n">
-        <v>6820433</v>
+        <v>6820406</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2926,10 +2926,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128601863</v>
+        <v>128601882</v>
       </c>
       <c r="B25" t="n">
-        <v>57686</v>
+        <v>79087</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2937,42 +2937,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>446183</v>
+        <v>446143</v>
       </c>
       <c r="R25" t="n">
-        <v>6820440</v>
+        <v>6820358</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3031,7 +3023,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128601882</v>
+        <v>128601876</v>
       </c>
       <c r="B26" t="n">
         <v>79087</v>
@@ -3066,10 +3058,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>446143</v>
+        <v>446231</v>
       </c>
       <c r="R26" t="n">
-        <v>6820358</v>
+        <v>6820457</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3128,10 +3120,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128601876</v>
+        <v>128601863</v>
       </c>
       <c r="B27" t="n">
-        <v>79087</v>
+        <v>57686</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3139,34 +3131,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>446231</v>
+        <v>446183</v>
       </c>
       <c r="R27" t="n">
-        <v>6820457</v>
+        <v>6820440</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3225,53 +3225,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128601866</v>
+        <v>128601871</v>
       </c>
       <c r="B28" t="n">
-        <v>57686</v>
+        <v>97460</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>446314</v>
+        <v>446191</v>
       </c>
       <c r="R28" t="n">
-        <v>6820495</v>
+        <v>6820410</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3330,45 +3322,53 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128601871</v>
+        <v>128601866</v>
       </c>
       <c r="B29" t="n">
-        <v>97460</v>
+        <v>57686</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>446191</v>
+        <v>446314</v>
       </c>
       <c r="R29" t="n">
-        <v>6820410</v>
+        <v>6820495</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>

--- a/artfynd/A 37730-2023 artfynd.xlsx
+++ b/artfynd/A 37730-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128601913</v>
       </c>
       <c r="B2" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128601912</v>
       </c>
       <c r="B3" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128601906</v>
       </c>
       <c r="B4" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128601904</v>
       </c>
       <c r="B5" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128601916</v>
       </c>
       <c r="B6" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128601907</v>
       </c>
       <c r="B7" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128601908</v>
       </c>
       <c r="B8" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>128601897</v>
       </c>
       <c r="B10" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>128601915</v>
       </c>
       <c r="B11" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>128601880</v>
       </c>
       <c r="B12" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1750,10 +1750,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128601862</v>
+        <v>128601881</v>
       </c>
       <c r="B13" t="n">
-        <v>57686</v>
+        <v>79089</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1761,42 +1761,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>446307</v>
+        <v>446035</v>
       </c>
       <c r="R13" t="n">
-        <v>6820425</v>
+        <v>6820374</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1855,32 +1847,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128601870</v>
+        <v>128601914</v>
       </c>
       <c r="B14" t="n">
-        <v>97460</v>
+        <v>79089</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1890,10 +1882,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>446224</v>
+        <v>446152</v>
       </c>
       <c r="R14" t="n">
-        <v>6820433</v>
+        <v>6820406</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1952,10 +1944,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128601881</v>
+        <v>128601862</v>
       </c>
       <c r="B15" t="n">
-        <v>79087</v>
+        <v>57686</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1963,34 +1955,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>446035</v>
+        <v>446307</v>
       </c>
       <c r="R15" t="n">
-        <v>6820374</v>
+        <v>6820425</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2049,32 +2049,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128601914</v>
+        <v>128601870</v>
       </c>
       <c r="B16" t="n">
-        <v>79087</v>
+        <v>97462</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2084,10 +2084,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>446152</v>
+        <v>446224</v>
       </c>
       <c r="R16" t="n">
-        <v>6820406</v>
+        <v>6820433</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2149,7 +2149,7 @@
         <v>128601921</v>
       </c>
       <c r="B17" t="n">
-        <v>90966</v>
+        <v>90968</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>128601919</v>
       </c>
       <c r="B18" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2344,10 +2344,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128601864</v>
+        <v>128601909</v>
       </c>
       <c r="B19" t="n">
-        <v>57686</v>
+        <v>79089</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2355,21 +2355,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2379,10 +2379,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>446223</v>
+        <v>446185</v>
       </c>
       <c r="R19" t="n">
-        <v>6820431</v>
+        <v>6820420</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2441,10 +2441,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128601909</v>
+        <v>128601864</v>
       </c>
       <c r="B20" t="n">
-        <v>79087</v>
+        <v>57686</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2452,21 +2452,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2476,10 +2476,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>446185</v>
+        <v>446223</v>
       </c>
       <c r="R20" t="n">
-        <v>6820420</v>
+        <v>6820431</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2541,7 +2541,7 @@
         <v>128601873</v>
       </c>
       <c r="B21" t="n">
-        <v>78845</v>
+        <v>78847</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>128601911</v>
       </c>
       <c r="B22" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
         <v>128601918</v>
       </c>
       <c r="B23" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>128601869</v>
       </c>
       <c r="B24" t="n">
-        <v>97460</v>
+        <v>97462</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         <v>128601882</v>
       </c>
       <c r="B25" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         <v>128601876</v>
       </c>
       <c r="B26" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3225,45 +3225,53 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128601871</v>
+        <v>128601866</v>
       </c>
       <c r="B28" t="n">
-        <v>97460</v>
+        <v>57686</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>446191</v>
+        <v>446314</v>
       </c>
       <c r="R28" t="n">
-        <v>6820410</v>
+        <v>6820495</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3322,53 +3330,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128601866</v>
+        <v>128601871</v>
       </c>
       <c r="B29" t="n">
-        <v>57686</v>
+        <v>97462</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>446314</v>
+        <v>446191</v>
       </c>
       <c r="R29" t="n">
-        <v>6820495</v>
+        <v>6820410</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3430,7 +3430,7 @@
         <v>128601917</v>
       </c>
       <c r="B30" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>128601903</v>
       </c>
       <c r="B31" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3624,7 +3624,7 @@
         <v>128601900</v>
       </c>
       <c r="B32" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3721,7 +3721,7 @@
         <v>128601905</v>
       </c>
       <c r="B33" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3818,7 +3818,7 @@
         <v>128601902</v>
       </c>
       <c r="B34" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3915,7 +3915,7 @@
         <v>128601899</v>
       </c>
       <c r="B35" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4012,7 +4012,7 @@
         <v>128601877</v>
       </c>
       <c r="B36" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4109,7 +4109,7 @@
         <v>128601879</v>
       </c>
       <c r="B37" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
         <v>128601910</v>
       </c>
       <c r="B38" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 37730-2023 artfynd.xlsx
+++ b/artfynd/A 37730-2023 artfynd.xlsx
@@ -1063,7 +1063,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128601916</v>
+        <v>128601907</v>
       </c>
       <c r="B6" t="n">
         <v>79089</v>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>446136</v>
+        <v>446217</v>
       </c>
       <c r="R6" t="n">
-        <v>6820361</v>
+        <v>6820443</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,7 +1160,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128601907</v>
+        <v>128601916</v>
       </c>
       <c r="B7" t="n">
         <v>79089</v>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>446217</v>
+        <v>446136</v>
       </c>
       <c r="R7" t="n">
-        <v>6820443</v>
+        <v>6820361</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1750,32 +1750,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128601881</v>
+        <v>128601870</v>
       </c>
       <c r="B13" t="n">
-        <v>79089</v>
+        <v>97462</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>446035</v>
+        <v>446224</v>
       </c>
       <c r="R13" t="n">
-        <v>6820374</v>
+        <v>6820433</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1847,10 +1847,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128601914</v>
+        <v>128601862</v>
       </c>
       <c r="B14" t="n">
-        <v>79089</v>
+        <v>57686</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1858,34 +1858,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>446152</v>
+        <v>446307</v>
       </c>
       <c r="R14" t="n">
-        <v>6820406</v>
+        <v>6820425</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1944,10 +1952,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128601862</v>
+        <v>128601881</v>
       </c>
       <c r="B15" t="n">
-        <v>57686</v>
+        <v>79089</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1955,42 +1963,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>446307</v>
+        <v>446035</v>
       </c>
       <c r="R15" t="n">
-        <v>6820425</v>
+        <v>6820374</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2049,32 +2049,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128601870</v>
+        <v>128601914</v>
       </c>
       <c r="B16" t="n">
-        <v>97462</v>
+        <v>79089</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2084,10 +2084,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>446224</v>
+        <v>446152</v>
       </c>
       <c r="R16" t="n">
-        <v>6820433</v>
+        <v>6820406</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2344,10 +2344,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128601909</v>
+        <v>128601864</v>
       </c>
       <c r="B19" t="n">
-        <v>79089</v>
+        <v>57686</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2355,21 +2355,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2379,10 +2379,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>446185</v>
+        <v>446223</v>
       </c>
       <c r="R19" t="n">
-        <v>6820420</v>
+        <v>6820431</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2441,10 +2441,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128601864</v>
+        <v>128601909</v>
       </c>
       <c r="B20" t="n">
-        <v>57686</v>
+        <v>79089</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2452,21 +2452,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2476,10 +2476,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>446223</v>
+        <v>446185</v>
       </c>
       <c r="R20" t="n">
-        <v>6820431</v>
+        <v>6820420</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2926,10 +2926,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128601882</v>
+        <v>128601863</v>
       </c>
       <c r="B25" t="n">
-        <v>79089</v>
+        <v>57686</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2937,34 +2937,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>446143</v>
+        <v>446183</v>
       </c>
       <c r="R25" t="n">
-        <v>6820358</v>
+        <v>6820440</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3023,7 +3031,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128601876</v>
+        <v>128601882</v>
       </c>
       <c r="B26" t="n">
         <v>79089</v>
@@ -3058,10 +3066,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>446231</v>
+        <v>446143</v>
       </c>
       <c r="R26" t="n">
-        <v>6820457</v>
+        <v>6820358</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3120,10 +3128,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128601863</v>
+        <v>128601876</v>
       </c>
       <c r="B27" t="n">
-        <v>57686</v>
+        <v>79089</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3131,42 +3139,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>446183</v>
+        <v>446231</v>
       </c>
       <c r="R27" t="n">
-        <v>6820440</v>
+        <v>6820457</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3815,7 +3815,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128601902</v>
+        <v>128601877</v>
       </c>
       <c r="B34" t="n">
         <v>79089</v>
@@ -3850,10 +3850,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>446302</v>
+        <v>446053</v>
       </c>
       <c r="R34" t="n">
-        <v>6820462</v>
+        <v>6820362</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4009,7 +4009,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128601877</v>
+        <v>128601902</v>
       </c>
       <c r="B36" t="n">
         <v>79089</v>
@@ -4044,10 +4044,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>446053</v>
+        <v>446302</v>
       </c>
       <c r="R36" t="n">
-        <v>6820362</v>
+        <v>6820462</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4106,7 +4106,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128601879</v>
+        <v>128601910</v>
       </c>
       <c r="B37" t="n">
         <v>79089</v>
@@ -4141,10 +4141,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>446049</v>
+        <v>446128</v>
       </c>
       <c r="R37" t="n">
-        <v>6820350</v>
+        <v>6820421</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4203,7 +4203,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128601910</v>
+        <v>128601879</v>
       </c>
       <c r="B38" t="n">
         <v>79089</v>
@@ -4238,10 +4238,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>446128</v>
+        <v>446049</v>
       </c>
       <c r="R38" t="n">
-        <v>6820421</v>
+        <v>6820350</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>

--- a/artfynd/A 37730-2023 artfynd.xlsx
+++ b/artfynd/A 37730-2023 artfynd.xlsx
@@ -966,7 +966,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128601904</v>
+        <v>128601916</v>
       </c>
       <c r="B5" t="n">
         <v>79089</v>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>446296</v>
+        <v>446136</v>
       </c>
       <c r="R5" t="n">
-        <v>6820423</v>
+        <v>6820361</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,7 +1063,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128601907</v>
+        <v>128601904</v>
       </c>
       <c r="B6" t="n">
         <v>79089</v>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>446217</v>
+        <v>446296</v>
       </c>
       <c r="R6" t="n">
-        <v>6820443</v>
+        <v>6820423</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,7 +1160,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128601916</v>
+        <v>128601907</v>
       </c>
       <c r="B7" t="n">
         <v>79089</v>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>446136</v>
+        <v>446217</v>
       </c>
       <c r="R7" t="n">
-        <v>6820361</v>
+        <v>6820443</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -3815,7 +3815,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128601877</v>
+        <v>128601902</v>
       </c>
       <c r="B34" t="n">
         <v>79089</v>
@@ -3850,10 +3850,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>446053</v>
+        <v>446302</v>
       </c>
       <c r="R34" t="n">
-        <v>6820362</v>
+        <v>6820462</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3912,7 +3912,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128601899</v>
+        <v>128601877</v>
       </c>
       <c r="B35" t="n">
         <v>79089</v>
@@ -3947,10 +3947,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>446477</v>
+        <v>446053</v>
       </c>
       <c r="R35" t="n">
-        <v>6820530</v>
+        <v>6820362</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4009,7 +4009,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128601902</v>
+        <v>128601899</v>
       </c>
       <c r="B36" t="n">
         <v>79089</v>
@@ -4044,10 +4044,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>446302</v>
+        <v>446477</v>
       </c>
       <c r="R36" t="n">
-        <v>6820462</v>
+        <v>6820530</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>

--- a/artfynd/A 37730-2023 artfynd.xlsx
+++ b/artfynd/A 37730-2023 artfynd.xlsx
@@ -966,7 +966,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128601916</v>
+        <v>128601904</v>
       </c>
       <c r="B5" t="n">
         <v>79089</v>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>446136</v>
+        <v>446296</v>
       </c>
       <c r="R5" t="n">
-        <v>6820361</v>
+        <v>6820423</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,7 +1063,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128601904</v>
+        <v>128601916</v>
       </c>
       <c r="B6" t="n">
         <v>79089</v>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>446296</v>
+        <v>446136</v>
       </c>
       <c r="R6" t="n">
-        <v>6820423</v>
+        <v>6820361</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1750,32 +1750,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128601870</v>
+        <v>128601881</v>
       </c>
       <c r="B13" t="n">
-        <v>97462</v>
+        <v>79089</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>446224</v>
+        <v>446035</v>
       </c>
       <c r="R13" t="n">
-        <v>6820433</v>
+        <v>6820374</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1847,10 +1847,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128601862</v>
+        <v>128601914</v>
       </c>
       <c r="B14" t="n">
-        <v>57686</v>
+        <v>79089</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1858,42 +1858,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>446307</v>
+        <v>446152</v>
       </c>
       <c r="R14" t="n">
-        <v>6820425</v>
+        <v>6820406</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1952,32 +1944,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128601881</v>
+        <v>128601870</v>
       </c>
       <c r="B15" t="n">
-        <v>79089</v>
+        <v>97463</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1987,10 +1979,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>446035</v>
+        <v>446224</v>
       </c>
       <c r="R15" t="n">
-        <v>6820374</v>
+        <v>6820433</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2049,10 +2041,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128601914</v>
+        <v>128601862</v>
       </c>
       <c r="B16" t="n">
-        <v>79089</v>
+        <v>57686</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2060,34 +2052,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>446152</v>
+        <v>446307</v>
       </c>
       <c r="R16" t="n">
-        <v>6820406</v>
+        <v>6820425</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2149,7 +2149,7 @@
         <v>128601921</v>
       </c>
       <c r="B17" t="n">
-        <v>90968</v>
+        <v>90969</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>128601869</v>
       </c>
       <c r="B24" t="n">
-        <v>97462</v>
+        <v>97463</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2926,10 +2926,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128601863</v>
+        <v>128601882</v>
       </c>
       <c r="B25" t="n">
-        <v>57686</v>
+        <v>79089</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2937,42 +2937,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>446183</v>
+        <v>446143</v>
       </c>
       <c r="R25" t="n">
-        <v>6820440</v>
+        <v>6820358</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3031,7 +3023,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128601882</v>
+        <v>128601876</v>
       </c>
       <c r="B26" t="n">
         <v>79089</v>
@@ -3066,10 +3058,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>446143</v>
+        <v>446231</v>
       </c>
       <c r="R26" t="n">
-        <v>6820358</v>
+        <v>6820457</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3128,10 +3120,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128601876</v>
+        <v>128601863</v>
       </c>
       <c r="B27" t="n">
-        <v>79089</v>
+        <v>57686</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3139,34 +3131,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>446231</v>
+        <v>446183</v>
       </c>
       <c r="R27" t="n">
-        <v>6820457</v>
+        <v>6820440</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3225,53 +3225,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128601866</v>
+        <v>128601871</v>
       </c>
       <c r="B28" t="n">
-        <v>57686</v>
+        <v>97463</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>446314</v>
+        <v>446191</v>
       </c>
       <c r="R28" t="n">
-        <v>6820495</v>
+        <v>6820410</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3330,45 +3322,53 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128601871</v>
+        <v>128601866</v>
       </c>
       <c r="B29" t="n">
-        <v>97462</v>
+        <v>57686</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>446191</v>
+        <v>446314</v>
       </c>
       <c r="R29" t="n">
-        <v>6820410</v>
+        <v>6820495</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3912,7 +3912,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128601877</v>
+        <v>128601899</v>
       </c>
       <c r="B35" t="n">
         <v>79089</v>
@@ -3947,10 +3947,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>446053</v>
+        <v>446477</v>
       </c>
       <c r="R35" t="n">
-        <v>6820362</v>
+        <v>6820530</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4009,7 +4009,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128601899</v>
+        <v>128601877</v>
       </c>
       <c r="B36" t="n">
         <v>79089</v>
@@ -4044,10 +4044,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>446477</v>
+        <v>446053</v>
       </c>
       <c r="R36" t="n">
-        <v>6820530</v>
+        <v>6820362</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4106,7 +4106,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128601910</v>
+        <v>128601879</v>
       </c>
       <c r="B37" t="n">
         <v>79089</v>
@@ -4141,10 +4141,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>446128</v>
+        <v>446049</v>
       </c>
       <c r="R37" t="n">
-        <v>6820421</v>
+        <v>6820350</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4203,7 +4203,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128601879</v>
+        <v>128601910</v>
       </c>
       <c r="B38" t="n">
         <v>79089</v>
@@ -4238,10 +4238,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>446049</v>
+        <v>446128</v>
       </c>
       <c r="R38" t="n">
-        <v>6820350</v>
+        <v>6820421</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>

--- a/artfynd/A 37730-2023 artfynd.xlsx
+++ b/artfynd/A 37730-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128601913</v>
       </c>
       <c r="B2" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128601912</v>
       </c>
       <c r="B3" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128601906</v>
       </c>
       <c r="B4" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128601904</v>
       </c>
       <c r="B5" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128601916</v>
       </c>
       <c r="B6" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128601907</v>
       </c>
       <c r="B7" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128601908</v>
       </c>
       <c r="B8" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128601865</v>
+        <v>128601897</v>
       </c>
       <c r="B9" t="n">
-        <v>57686</v>
+        <v>79116</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,42 +1365,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>446361</v>
+        <v>446488</v>
       </c>
       <c r="R9" t="n">
-        <v>6820513</v>
+        <v>6820524</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1459,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128601897</v>
+        <v>128601865</v>
       </c>
       <c r="B10" t="n">
-        <v>79089</v>
+        <v>57713</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1470,34 +1462,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>446488</v>
+        <v>446361</v>
       </c>
       <c r="R10" t="n">
-        <v>6820524</v>
+        <v>6820513</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1559,7 +1559,7 @@
         <v>128601915</v>
       </c>
       <c r="B11" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>128601880</v>
       </c>
       <c r="B12" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1750,32 +1750,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128601881</v>
+        <v>128601870</v>
       </c>
       <c r="B13" t="n">
-        <v>79089</v>
+        <v>97490</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>446035</v>
+        <v>446224</v>
       </c>
       <c r="R13" t="n">
-        <v>6820374</v>
+        <v>6820433</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1847,10 +1847,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128601914</v>
+        <v>128601881</v>
       </c>
       <c r="B14" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>446152</v>
+        <v>446035</v>
       </c>
       <c r="R14" t="n">
-        <v>6820406</v>
+        <v>6820374</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1944,32 +1944,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128601870</v>
+        <v>128601914</v>
       </c>
       <c r="B15" t="n">
-        <v>97463</v>
+        <v>79116</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1979,10 +1979,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>446224</v>
+        <v>446152</v>
       </c>
       <c r="R15" t="n">
-        <v>6820433</v>
+        <v>6820406</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2044,7 +2044,7 @@
         <v>128601862</v>
       </c>
       <c r="B16" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>128601921</v>
       </c>
       <c r="B17" t="n">
-        <v>90969</v>
+        <v>90996</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>128601919</v>
       </c>
       <c r="B18" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
         <v>128601864</v>
       </c>
       <c r="B19" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2441,10 +2441,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128601909</v>
+        <v>128601873</v>
       </c>
       <c r="B20" t="n">
-        <v>79089</v>
+        <v>78874</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2452,21 +2452,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2476,10 +2476,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>446185</v>
+        <v>446106</v>
       </c>
       <c r="R20" t="n">
-        <v>6820420</v>
+        <v>6820399</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2538,10 +2538,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128601873</v>
+        <v>128601909</v>
       </c>
       <c r="B21" t="n">
-        <v>78847</v>
+        <v>79116</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2549,21 +2549,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>446106</v>
+        <v>446185</v>
       </c>
       <c r="R21" t="n">
-        <v>6820399</v>
+        <v>6820420</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2638,7 +2638,7 @@
         <v>128601911</v>
       </c>
       <c r="B22" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
         <v>128601918</v>
       </c>
       <c r="B23" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>128601869</v>
       </c>
       <c r="B24" t="n">
-        <v>97463</v>
+        <v>97490</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         <v>128601882</v>
       </c>
       <c r="B25" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         <v>128601876</v>
       </c>
       <c r="B26" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>128601863</v>
       </c>
       <c r="B27" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3225,45 +3225,53 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128601871</v>
+        <v>128601866</v>
       </c>
       <c r="B28" t="n">
-        <v>97463</v>
+        <v>57713</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>446191</v>
+        <v>446314</v>
       </c>
       <c r="R28" t="n">
-        <v>6820410</v>
+        <v>6820495</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3322,53 +3330,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128601866</v>
+        <v>128601871</v>
       </c>
       <c r="B29" t="n">
-        <v>57686</v>
+        <v>97490</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>446314</v>
+        <v>446191</v>
       </c>
       <c r="R29" t="n">
-        <v>6820495</v>
+        <v>6820410</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3430,7 +3430,7 @@
         <v>128601917</v>
       </c>
       <c r="B30" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>128601903</v>
       </c>
       <c r="B31" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3624,7 +3624,7 @@
         <v>128601900</v>
       </c>
       <c r="B32" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3721,7 +3721,7 @@
         <v>128601905</v>
       </c>
       <c r="B33" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3818,7 +3818,7 @@
         <v>128601902</v>
       </c>
       <c r="B34" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3915,7 +3915,7 @@
         <v>128601899</v>
       </c>
       <c r="B35" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4012,7 +4012,7 @@
         <v>128601877</v>
       </c>
       <c r="B36" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4109,7 +4109,7 @@
         <v>128601879</v>
       </c>
       <c r="B37" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
         <v>128601910</v>
       </c>
       <c r="B38" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 37730-2023 artfynd.xlsx
+++ b/artfynd/A 37730-2023 artfynd.xlsx
@@ -2344,10 +2344,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128601864</v>
+        <v>128601909</v>
       </c>
       <c r="B19" t="n">
-        <v>57713</v>
+        <v>79116</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2355,21 +2355,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2379,10 +2379,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>446223</v>
+        <v>446185</v>
       </c>
       <c r="R19" t="n">
-        <v>6820431</v>
+        <v>6820420</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2441,10 +2441,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128601873</v>
+        <v>128601864</v>
       </c>
       <c r="B20" t="n">
-        <v>78874</v>
+        <v>57713</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2452,21 +2452,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2476,10 +2476,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>446106</v>
+        <v>446223</v>
       </c>
       <c r="R20" t="n">
-        <v>6820399</v>
+        <v>6820431</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2538,10 +2538,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128601909</v>
+        <v>128601873</v>
       </c>
       <c r="B21" t="n">
-        <v>79116</v>
+        <v>78874</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2549,21 +2549,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>446185</v>
+        <v>446106</v>
       </c>
       <c r="R21" t="n">
-        <v>6820420</v>
+        <v>6820399</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3815,7 +3815,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128601902</v>
+        <v>128601899</v>
       </c>
       <c r="B34" t="n">
         <v>79116</v>
@@ -3850,10 +3850,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>446302</v>
+        <v>446477</v>
       </c>
       <c r="R34" t="n">
-        <v>6820462</v>
+        <v>6820530</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3912,7 +3912,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128601899</v>
+        <v>128601902</v>
       </c>
       <c r="B35" t="n">
         <v>79116</v>
@@ -3947,10 +3947,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>446477</v>
+        <v>446302</v>
       </c>
       <c r="R35" t="n">
-        <v>6820530</v>
+        <v>6820462</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>

--- a/artfynd/A 37730-2023 artfynd.xlsx
+++ b/artfynd/A 37730-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128601913</v>
       </c>
       <c r="B2" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128601912</v>
       </c>
       <c r="B3" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128601906</v>
       </c>
       <c r="B4" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128601904</v>
       </c>
       <c r="B5" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128601916</v>
       </c>
       <c r="B6" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128601907</v>
       </c>
       <c r="B7" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128601908</v>
       </c>
       <c r="B8" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128601897</v>
+        <v>128601865</v>
       </c>
       <c r="B9" t="n">
-        <v>79116</v>
+        <v>57713</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,34 +1365,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>446488</v>
+        <v>446361</v>
       </c>
       <c r="R9" t="n">
-        <v>6820524</v>
+        <v>6820513</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,10 +1459,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128601865</v>
+        <v>128601897</v>
       </c>
       <c r="B10" t="n">
-        <v>57713</v>
+        <v>79120</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,42 +1470,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>446361</v>
+        <v>446488</v>
       </c>
       <c r="R10" t="n">
-        <v>6820513</v>
+        <v>6820524</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1559,7 +1559,7 @@
         <v>128601915</v>
       </c>
       <c r="B11" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>128601880</v>
       </c>
       <c r="B12" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>128601870</v>
       </c>
       <c r="B13" t="n">
-        <v>97490</v>
+        <v>97496</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>128601881</v>
       </c>
       <c r="B14" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>128601914</v>
       </c>
       <c r="B15" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>128601921</v>
       </c>
       <c r="B17" t="n">
-        <v>90996</v>
+        <v>91001</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>128601919</v>
       </c>
       <c r="B18" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2344,10 +2344,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128601909</v>
+        <v>128601873</v>
       </c>
       <c r="B19" t="n">
-        <v>79116</v>
+        <v>78878</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2355,21 +2355,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2379,10 +2379,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>446185</v>
+        <v>446106</v>
       </c>
       <c r="R19" t="n">
-        <v>6820420</v>
+        <v>6820399</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2441,10 +2441,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128601864</v>
+        <v>128601909</v>
       </c>
       <c r="B20" t="n">
-        <v>57713</v>
+        <v>79120</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2452,21 +2452,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2476,10 +2476,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>446223</v>
+        <v>446185</v>
       </c>
       <c r="R20" t="n">
-        <v>6820431</v>
+        <v>6820420</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2538,10 +2538,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128601873</v>
+        <v>128601864</v>
       </c>
       <c r="B21" t="n">
-        <v>78874</v>
+        <v>57713</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2549,21 +2549,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>446106</v>
+        <v>446223</v>
       </c>
       <c r="R21" t="n">
-        <v>6820399</v>
+        <v>6820431</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2638,7 +2638,7 @@
         <v>128601911</v>
       </c>
       <c r="B22" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
         <v>128601918</v>
       </c>
       <c r="B23" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>128601869</v>
       </c>
       <c r="B24" t="n">
-        <v>97490</v>
+        <v>97496</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2926,10 +2926,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128601882</v>
+        <v>128601863</v>
       </c>
       <c r="B25" t="n">
-        <v>79116</v>
+        <v>57713</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2937,34 +2937,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>446143</v>
+        <v>446183</v>
       </c>
       <c r="R25" t="n">
-        <v>6820358</v>
+        <v>6820440</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3023,10 +3031,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128601876</v>
+        <v>128601882</v>
       </c>
       <c r="B26" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3058,10 +3066,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>446231</v>
+        <v>446143</v>
       </c>
       <c r="R26" t="n">
-        <v>6820457</v>
+        <v>6820358</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3120,10 +3128,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128601863</v>
+        <v>128601876</v>
       </c>
       <c r="B27" t="n">
-        <v>57713</v>
+        <v>79120</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3131,42 +3139,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>446183</v>
+        <v>446231</v>
       </c>
       <c r="R27" t="n">
-        <v>6820440</v>
+        <v>6820457</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3333,7 +3333,7 @@
         <v>128601871</v>
       </c>
       <c r="B29" t="n">
-        <v>97490</v>
+        <v>97496</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>128601917</v>
       </c>
       <c r="B30" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>128601903</v>
       </c>
       <c r="B31" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3624,7 +3624,7 @@
         <v>128601900</v>
       </c>
       <c r="B32" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3721,7 +3721,7 @@
         <v>128601905</v>
       </c>
       <c r="B33" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3815,10 +3815,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128601899</v>
+        <v>128601902</v>
       </c>
       <c r="B34" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3850,10 +3850,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>446477</v>
+        <v>446302</v>
       </c>
       <c r="R34" t="n">
-        <v>6820530</v>
+        <v>6820462</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3912,10 +3912,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128601902</v>
+        <v>128601899</v>
       </c>
       <c r="B35" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3947,10 +3947,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>446302</v>
+        <v>446477</v>
       </c>
       <c r="R35" t="n">
-        <v>6820462</v>
+        <v>6820530</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4012,7 +4012,7 @@
         <v>128601877</v>
       </c>
       <c r="B36" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4109,7 +4109,7 @@
         <v>128601879</v>
       </c>
       <c r="B37" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
         <v>128601910</v>
       </c>
       <c r="B38" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 37730-2023 artfynd.xlsx
+++ b/artfynd/A 37730-2023 artfynd.xlsx
@@ -1750,32 +1750,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128601870</v>
+        <v>128601881</v>
       </c>
       <c r="B13" t="n">
-        <v>97496</v>
+        <v>79120</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>446224</v>
+        <v>446035</v>
       </c>
       <c r="R13" t="n">
-        <v>6820433</v>
+        <v>6820374</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1847,7 +1847,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128601881</v>
+        <v>128601914</v>
       </c>
       <c r="B14" t="n">
         <v>79120</v>
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>446035</v>
+        <v>446152</v>
       </c>
       <c r="R14" t="n">
-        <v>6820374</v>
+        <v>6820406</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1944,10 +1944,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128601914</v>
+        <v>128601862</v>
       </c>
       <c r="B15" t="n">
-        <v>79120</v>
+        <v>57713</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1955,34 +1955,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>446152</v>
+        <v>446307</v>
       </c>
       <c r="R15" t="n">
-        <v>6820406</v>
+        <v>6820425</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2041,53 +2049,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128601862</v>
+        <v>128601870</v>
       </c>
       <c r="B16" t="n">
-        <v>57713</v>
+        <v>97503</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>446307</v>
+        <v>446224</v>
       </c>
       <c r="R16" t="n">
-        <v>6820425</v>
+        <v>6820433</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2149,7 +2149,7 @@
         <v>128601921</v>
       </c>
       <c r="B17" t="n">
-        <v>91001</v>
+        <v>91006</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2344,10 +2344,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128601873</v>
+        <v>128601909</v>
       </c>
       <c r="B19" t="n">
-        <v>78878</v>
+        <v>79120</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2355,21 +2355,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2379,10 +2379,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>446106</v>
+        <v>446185</v>
       </c>
       <c r="R19" t="n">
-        <v>6820399</v>
+        <v>6820420</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2441,10 +2441,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128601909</v>
+        <v>128601864</v>
       </c>
       <c r="B20" t="n">
-        <v>79120</v>
+        <v>57713</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2452,21 +2452,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2476,10 +2476,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>446185</v>
+        <v>446223</v>
       </c>
       <c r="R20" t="n">
-        <v>6820420</v>
+        <v>6820431</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2538,10 +2538,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128601864</v>
+        <v>128601873</v>
       </c>
       <c r="B21" t="n">
-        <v>57713</v>
+        <v>78878</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2549,21 +2549,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>446223</v>
+        <v>446106</v>
       </c>
       <c r="R21" t="n">
-        <v>6820431</v>
+        <v>6820399</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2832,7 +2832,7 @@
         <v>128601869</v>
       </c>
       <c r="B24" t="n">
-        <v>97496</v>
+        <v>97503</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2926,10 +2926,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128601863</v>
+        <v>128601882</v>
       </c>
       <c r="B25" t="n">
-        <v>57713</v>
+        <v>79120</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2937,42 +2937,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>446183</v>
+        <v>446143</v>
       </c>
       <c r="R25" t="n">
-        <v>6820440</v>
+        <v>6820358</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3031,7 +3023,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128601882</v>
+        <v>128601876</v>
       </c>
       <c r="B26" t="n">
         <v>79120</v>
@@ -3066,10 +3058,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>446143</v>
+        <v>446231</v>
       </c>
       <c r="R26" t="n">
-        <v>6820358</v>
+        <v>6820457</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3128,10 +3120,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128601876</v>
+        <v>128601863</v>
       </c>
       <c r="B27" t="n">
-        <v>79120</v>
+        <v>57713</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3139,34 +3131,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>446231</v>
+        <v>446183</v>
       </c>
       <c r="R27" t="n">
-        <v>6820457</v>
+        <v>6820440</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3333,7 +3333,7 @@
         <v>128601871</v>
       </c>
       <c r="B29" t="n">
-        <v>97496</v>
+        <v>97503</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 37730-2023 artfynd.xlsx
+++ b/artfynd/A 37730-2023 artfynd.xlsx
@@ -1750,7 +1750,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128601881</v>
+        <v>128601914</v>
       </c>
       <c r="B13" t="n">
         <v>79120</v>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>446035</v>
+        <v>446152</v>
       </c>
       <c r="R13" t="n">
-        <v>6820374</v>
+        <v>6820406</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1847,7 +1847,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128601914</v>
+        <v>128601881</v>
       </c>
       <c r="B14" t="n">
         <v>79120</v>
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>446152</v>
+        <v>446035</v>
       </c>
       <c r="R14" t="n">
-        <v>6820406</v>
+        <v>6820374</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2344,10 +2344,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128601909</v>
+        <v>128601873</v>
       </c>
       <c r="B19" t="n">
-        <v>79120</v>
+        <v>78878</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2355,21 +2355,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2379,10 +2379,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>446185</v>
+        <v>446106</v>
       </c>
       <c r="R19" t="n">
-        <v>6820420</v>
+        <v>6820399</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2441,10 +2441,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128601864</v>
+        <v>128601909</v>
       </c>
       <c r="B20" t="n">
-        <v>57713</v>
+        <v>79120</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2452,21 +2452,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2476,10 +2476,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>446223</v>
+        <v>446185</v>
       </c>
       <c r="R20" t="n">
-        <v>6820431</v>
+        <v>6820420</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2538,10 +2538,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128601873</v>
+        <v>128601864</v>
       </c>
       <c r="B21" t="n">
-        <v>78878</v>
+        <v>57713</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2549,21 +2549,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>446106</v>
+        <v>446223</v>
       </c>
       <c r="R21" t="n">
-        <v>6820399</v>
+        <v>6820431</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2926,10 +2926,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128601882</v>
+        <v>128601863</v>
       </c>
       <c r="B25" t="n">
-        <v>79120</v>
+        <v>57713</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2937,34 +2937,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>446143</v>
+        <v>446183</v>
       </c>
       <c r="R25" t="n">
-        <v>6820358</v>
+        <v>6820440</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3023,7 +3031,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128601876</v>
+        <v>128601882</v>
       </c>
       <c r="B26" t="n">
         <v>79120</v>
@@ -3058,10 +3066,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>446231</v>
+        <v>446143</v>
       </c>
       <c r="R26" t="n">
-        <v>6820457</v>
+        <v>6820358</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3120,10 +3128,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128601863</v>
+        <v>128601876</v>
       </c>
       <c r="B27" t="n">
-        <v>57713</v>
+        <v>79120</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3131,42 +3139,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>446183</v>
+        <v>446231</v>
       </c>
       <c r="R27" t="n">
-        <v>6820440</v>
+        <v>6820457</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3225,53 +3225,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128601866</v>
+        <v>128601871</v>
       </c>
       <c r="B28" t="n">
-        <v>57713</v>
+        <v>97503</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>446314</v>
+        <v>446191</v>
       </c>
       <c r="R28" t="n">
-        <v>6820495</v>
+        <v>6820410</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3330,45 +3322,53 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128601871</v>
+        <v>128601866</v>
       </c>
       <c r="B29" t="n">
-        <v>97503</v>
+        <v>57713</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>446191</v>
+        <v>446314</v>
       </c>
       <c r="R29" t="n">
-        <v>6820410</v>
+        <v>6820495</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3718,7 +3718,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128601905</v>
+        <v>128601902</v>
       </c>
       <c r="B33" t="n">
         <v>79120</v>
@@ -3753,10 +3753,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>446304</v>
+        <v>446302</v>
       </c>
       <c r="R33" t="n">
-        <v>6820419</v>
+        <v>6820462</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3815,7 +3815,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128601902</v>
+        <v>128601877</v>
       </c>
       <c r="B34" t="n">
         <v>79120</v>
@@ -3850,10 +3850,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>446302</v>
+        <v>446053</v>
       </c>
       <c r="R34" t="n">
-        <v>6820462</v>
+        <v>6820362</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3912,7 +3912,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128601899</v>
+        <v>128601905</v>
       </c>
       <c r="B35" t="n">
         <v>79120</v>
@@ -3947,10 +3947,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>446477</v>
+        <v>446304</v>
       </c>
       <c r="R35" t="n">
-        <v>6820530</v>
+        <v>6820419</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4009,7 +4009,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128601877</v>
+        <v>128601899</v>
       </c>
       <c r="B36" t="n">
         <v>79120</v>
@@ -4044,10 +4044,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>446053</v>
+        <v>446477</v>
       </c>
       <c r="R36" t="n">
-        <v>6820362</v>
+        <v>6820530</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>

--- a/artfynd/A 37730-2023 artfynd.xlsx
+++ b/artfynd/A 37730-2023 artfynd.xlsx
@@ -1750,32 +1750,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128601914</v>
+        <v>128601870</v>
       </c>
       <c r="B13" t="n">
-        <v>79120</v>
+        <v>97503</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>446152</v>
+        <v>446224</v>
       </c>
       <c r="R13" t="n">
-        <v>6820406</v>
+        <v>6820433</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1847,7 +1847,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128601881</v>
+        <v>128601914</v>
       </c>
       <c r="B14" t="n">
         <v>79120</v>
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>446035</v>
+        <v>446152</v>
       </c>
       <c r="R14" t="n">
-        <v>6820374</v>
+        <v>6820406</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1944,10 +1944,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128601862</v>
+        <v>128601881</v>
       </c>
       <c r="B15" t="n">
-        <v>57713</v>
+        <v>79120</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1955,42 +1955,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>446307</v>
+        <v>446035</v>
       </c>
       <c r="R15" t="n">
-        <v>6820425</v>
+        <v>6820374</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2049,45 +2041,53 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128601870</v>
+        <v>128601862</v>
       </c>
       <c r="B16" t="n">
-        <v>97503</v>
+        <v>57713</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>446224</v>
+        <v>446307</v>
       </c>
       <c r="R16" t="n">
-        <v>6820433</v>
+        <v>6820425</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2635,32 +2635,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128601911</v>
+        <v>128601869</v>
       </c>
       <c r="B22" t="n">
-        <v>79120</v>
+        <v>97503</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2670,10 +2670,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>446097</v>
+        <v>446357</v>
       </c>
       <c r="R22" t="n">
-        <v>6820410</v>
+        <v>6820512</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2732,7 +2732,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128601918</v>
+        <v>128601911</v>
       </c>
       <c r="B23" t="n">
         <v>79120</v>
@@ -2767,10 +2767,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>446114</v>
+        <v>446097</v>
       </c>
       <c r="R23" t="n">
-        <v>6820373</v>
+        <v>6820410</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2829,32 +2829,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128601869</v>
+        <v>128601918</v>
       </c>
       <c r="B24" t="n">
-        <v>97503</v>
+        <v>79120</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2864,10 +2864,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>446357</v>
+        <v>446114</v>
       </c>
       <c r="R24" t="n">
-        <v>6820512</v>
+        <v>6820373</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2926,10 +2926,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128601863</v>
+        <v>128601882</v>
       </c>
       <c r="B25" t="n">
-        <v>57713</v>
+        <v>79120</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2937,42 +2937,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>446183</v>
+        <v>446143</v>
       </c>
       <c r="R25" t="n">
-        <v>6820440</v>
+        <v>6820358</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3031,7 +3023,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128601882</v>
+        <v>128601876</v>
       </c>
       <c r="B26" t="n">
         <v>79120</v>
@@ -3066,10 +3058,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>446143</v>
+        <v>446231</v>
       </c>
       <c r="R26" t="n">
-        <v>6820358</v>
+        <v>6820457</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3128,10 +3120,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128601876</v>
+        <v>128601863</v>
       </c>
       <c r="B27" t="n">
-        <v>79120</v>
+        <v>57713</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3139,34 +3131,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>446231</v>
+        <v>446183</v>
       </c>
       <c r="R27" t="n">
-        <v>6820457</v>
+        <v>6820440</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3718,7 +3718,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128601902</v>
+        <v>128601905</v>
       </c>
       <c r="B33" t="n">
         <v>79120</v>
@@ -3753,10 +3753,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>446302</v>
+        <v>446304</v>
       </c>
       <c r="R33" t="n">
-        <v>6820462</v>
+        <v>6820419</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3815,7 +3815,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128601877</v>
+        <v>128601899</v>
       </c>
       <c r="B34" t="n">
         <v>79120</v>
@@ -3850,10 +3850,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>446053</v>
+        <v>446477</v>
       </c>
       <c r="R34" t="n">
-        <v>6820362</v>
+        <v>6820530</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3912,7 +3912,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128601905</v>
+        <v>128601902</v>
       </c>
       <c r="B35" t="n">
         <v>79120</v>
@@ -3947,10 +3947,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>446304</v>
+        <v>446302</v>
       </c>
       <c r="R35" t="n">
-        <v>6820419</v>
+        <v>6820462</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4009,7 +4009,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128601899</v>
+        <v>128601877</v>
       </c>
       <c r="B36" t="n">
         <v>79120</v>
@@ -4044,10 +4044,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>446477</v>
+        <v>446053</v>
       </c>
       <c r="R36" t="n">
-        <v>6820530</v>
+        <v>6820362</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>

--- a/artfynd/A 37730-2023 artfynd.xlsx
+++ b/artfynd/A 37730-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128601913</v>
       </c>
       <c r="B2" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128601912</v>
       </c>
       <c r="B3" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128601906</v>
       </c>
       <c r="B4" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128601904</v>
       </c>
       <c r="B5" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128601916</v>
       </c>
       <c r="B6" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128601907</v>
       </c>
       <c r="B7" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128601908</v>
       </c>
       <c r="B8" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128601865</v>
+        <v>128601897</v>
       </c>
       <c r="B9" t="n">
-        <v>57713</v>
+        <v>79124</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,42 +1365,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>446361</v>
+        <v>446488</v>
       </c>
       <c r="R9" t="n">
-        <v>6820513</v>
+        <v>6820524</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1459,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128601897</v>
+        <v>128601865</v>
       </c>
       <c r="B10" t="n">
-        <v>79120</v>
+        <v>57717</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1470,34 +1462,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>446488</v>
+        <v>446361</v>
       </c>
       <c r="R10" t="n">
-        <v>6820524</v>
+        <v>6820513</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1559,7 +1559,7 @@
         <v>128601915</v>
       </c>
       <c r="B11" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>128601880</v>
       </c>
       <c r="B12" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>128601870</v>
       </c>
       <c r="B13" t="n">
-        <v>97503</v>
+        <v>97507</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1847,10 +1847,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128601914</v>
+        <v>128601881</v>
       </c>
       <c r="B14" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>446152</v>
+        <v>446035</v>
       </c>
       <c r="R14" t="n">
-        <v>6820406</v>
+        <v>6820374</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1944,10 +1944,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128601881</v>
+        <v>128601914</v>
       </c>
       <c r="B15" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1979,10 +1979,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>446035</v>
+        <v>446152</v>
       </c>
       <c r="R15" t="n">
-        <v>6820374</v>
+        <v>6820406</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2044,7 +2044,7 @@
         <v>128601862</v>
       </c>
       <c r="B16" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>128601921</v>
       </c>
       <c r="B17" t="n">
-        <v>91006</v>
+        <v>91010</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>128601919</v>
       </c>
       <c r="B18" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2344,10 +2344,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128601873</v>
+        <v>128601909</v>
       </c>
       <c r="B19" t="n">
-        <v>78878</v>
+        <v>79124</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2355,21 +2355,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2379,10 +2379,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>446106</v>
+        <v>446185</v>
       </c>
       <c r="R19" t="n">
-        <v>6820399</v>
+        <v>6820420</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2441,10 +2441,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128601909</v>
+        <v>128601873</v>
       </c>
       <c r="B20" t="n">
-        <v>79120</v>
+        <v>78882</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2452,21 +2452,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2476,10 +2476,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>446185</v>
+        <v>446106</v>
       </c>
       <c r="R20" t="n">
-        <v>6820420</v>
+        <v>6820399</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2541,7 +2541,7 @@
         <v>128601864</v>
       </c>
       <c r="B21" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>128601869</v>
       </c>
       <c r="B22" t="n">
-        <v>97503</v>
+        <v>97507</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
         <v>128601911</v>
       </c>
       <c r="B23" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>128601918</v>
       </c>
       <c r="B24" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2926,10 +2926,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128601882</v>
+        <v>128601863</v>
       </c>
       <c r="B25" t="n">
-        <v>79120</v>
+        <v>57717</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2937,34 +2937,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>446143</v>
+        <v>446183</v>
       </c>
       <c r="R25" t="n">
-        <v>6820358</v>
+        <v>6820440</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3023,10 +3031,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128601876</v>
+        <v>128601882</v>
       </c>
       <c r="B26" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3058,10 +3066,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>446231</v>
+        <v>446143</v>
       </c>
       <c r="R26" t="n">
-        <v>6820457</v>
+        <v>6820358</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3120,10 +3128,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128601863</v>
+        <v>128601876</v>
       </c>
       <c r="B27" t="n">
-        <v>57713</v>
+        <v>79124</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3131,42 +3139,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>446183</v>
+        <v>446231</v>
       </c>
       <c r="R27" t="n">
-        <v>6820440</v>
+        <v>6820457</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3225,45 +3225,53 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128601871</v>
+        <v>128601866</v>
       </c>
       <c r="B28" t="n">
-        <v>97503</v>
+        <v>57717</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>446191</v>
+        <v>446314</v>
       </c>
       <c r="R28" t="n">
-        <v>6820410</v>
+        <v>6820495</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3322,53 +3330,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128601866</v>
+        <v>128601871</v>
       </c>
       <c r="B29" t="n">
-        <v>57713</v>
+        <v>97507</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>446314</v>
+        <v>446191</v>
       </c>
       <c r="R29" t="n">
-        <v>6820495</v>
+        <v>6820410</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3430,7 +3430,7 @@
         <v>128601917</v>
       </c>
       <c r="B30" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>128601903</v>
       </c>
       <c r="B31" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3624,7 +3624,7 @@
         <v>128601900</v>
       </c>
       <c r="B32" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3721,7 +3721,7 @@
         <v>128601905</v>
       </c>
       <c r="B33" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3815,10 +3815,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128601899</v>
+        <v>128601902</v>
       </c>
       <c r="B34" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3850,10 +3850,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>446477</v>
+        <v>446302</v>
       </c>
       <c r="R34" t="n">
-        <v>6820530</v>
+        <v>6820462</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3912,10 +3912,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128601902</v>
+        <v>128601899</v>
       </c>
       <c r="B35" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3947,10 +3947,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>446302</v>
+        <v>446477</v>
       </c>
       <c r="R35" t="n">
-        <v>6820462</v>
+        <v>6820530</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4012,7 +4012,7 @@
         <v>128601877</v>
       </c>
       <c r="B36" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4109,7 +4109,7 @@
         <v>128601879</v>
       </c>
       <c r="B37" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
         <v>128601910</v>
       </c>
       <c r="B38" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 37730-2023 artfynd.xlsx
+++ b/artfynd/A 37730-2023 artfynd.xlsx
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128601912</v>
+        <v>128601906</v>
       </c>
       <c r="B3" t="n">
         <v>79124</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446116</v>
+        <v>446239</v>
       </c>
       <c r="R3" t="n">
-        <v>6820405</v>
+        <v>6820451</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128601906</v>
+        <v>128601912</v>
       </c>
       <c r="B4" t="n">
         <v>79124</v>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>446239</v>
+        <v>446116</v>
       </c>
       <c r="R4" t="n">
-        <v>6820451</v>
+        <v>6820405</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1750,32 +1750,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128601870</v>
+        <v>128601881</v>
       </c>
       <c r="B13" t="n">
-        <v>97507</v>
+        <v>79124</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>446224</v>
+        <v>446035</v>
       </c>
       <c r="R13" t="n">
-        <v>6820433</v>
+        <v>6820374</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1847,7 +1847,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128601881</v>
+        <v>128601914</v>
       </c>
       <c r="B14" t="n">
         <v>79124</v>
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>446035</v>
+        <v>446152</v>
       </c>
       <c r="R14" t="n">
-        <v>6820374</v>
+        <v>6820406</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1944,10 +1944,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128601914</v>
+        <v>128601862</v>
       </c>
       <c r="B15" t="n">
-        <v>79124</v>
+        <v>57717</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1955,34 +1955,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>446152</v>
+        <v>446307</v>
       </c>
       <c r="R15" t="n">
-        <v>6820406</v>
+        <v>6820425</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2041,53 +2049,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128601862</v>
+        <v>128601870</v>
       </c>
       <c r="B16" t="n">
-        <v>57717</v>
+        <v>97507</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>446307</v>
+        <v>446224</v>
       </c>
       <c r="R16" t="n">
-        <v>6820425</v>
+        <v>6820433</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2441,10 +2441,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128601873</v>
+        <v>128601864</v>
       </c>
       <c r="B20" t="n">
-        <v>78882</v>
+        <v>57717</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2452,21 +2452,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2476,10 +2476,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>446106</v>
+        <v>446223</v>
       </c>
       <c r="R20" t="n">
-        <v>6820399</v>
+        <v>6820431</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2538,10 +2538,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128601864</v>
+        <v>128601873</v>
       </c>
       <c r="B21" t="n">
-        <v>57717</v>
+        <v>78882</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2549,21 +2549,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>446223</v>
+        <v>446106</v>
       </c>
       <c r="R21" t="n">
-        <v>6820431</v>
+        <v>6820399</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2635,32 +2635,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128601869</v>
+        <v>128601918</v>
       </c>
       <c r="B22" t="n">
-        <v>97507</v>
+        <v>79124</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2670,10 +2670,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>446357</v>
+        <v>446114</v>
       </c>
       <c r="R22" t="n">
-        <v>6820512</v>
+        <v>6820373</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2829,32 +2829,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128601918</v>
+        <v>128601869</v>
       </c>
       <c r="B24" t="n">
-        <v>79124</v>
+        <v>97507</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2864,10 +2864,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>446114</v>
+        <v>446357</v>
       </c>
       <c r="R24" t="n">
-        <v>6820373</v>
+        <v>6820512</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2926,10 +2926,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128601863</v>
+        <v>128601882</v>
       </c>
       <c r="B25" t="n">
-        <v>57717</v>
+        <v>79124</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2937,42 +2937,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>446183</v>
+        <v>446143</v>
       </c>
       <c r="R25" t="n">
-        <v>6820440</v>
+        <v>6820358</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3031,7 +3023,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128601882</v>
+        <v>128601876</v>
       </c>
       <c r="B26" t="n">
         <v>79124</v>
@@ -3066,10 +3058,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>446143</v>
+        <v>446231</v>
       </c>
       <c r="R26" t="n">
-        <v>6820358</v>
+        <v>6820457</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3128,10 +3120,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128601876</v>
+        <v>128601863</v>
       </c>
       <c r="B27" t="n">
-        <v>79124</v>
+        <v>57717</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3139,34 +3131,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>446231</v>
+        <v>446183</v>
       </c>
       <c r="R27" t="n">
-        <v>6820457</v>
+        <v>6820440</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3225,53 +3225,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128601866</v>
+        <v>128601871</v>
       </c>
       <c r="B28" t="n">
-        <v>57717</v>
+        <v>97507</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>446314</v>
+        <v>446191</v>
       </c>
       <c r="R28" t="n">
-        <v>6820495</v>
+        <v>6820410</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3330,45 +3322,53 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128601871</v>
+        <v>128601866</v>
       </c>
       <c r="B29" t="n">
-        <v>97507</v>
+        <v>57717</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>446191</v>
+        <v>446314</v>
       </c>
       <c r="R29" t="n">
-        <v>6820410</v>
+        <v>6820495</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>

--- a/artfynd/A 37730-2023 artfynd.xlsx
+++ b/artfynd/A 37730-2023 artfynd.xlsx
@@ -1063,7 +1063,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128601916</v>
+        <v>128601907</v>
       </c>
       <c r="B6" t="n">
         <v>79124</v>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>446136</v>
+        <v>446217</v>
       </c>
       <c r="R6" t="n">
-        <v>6820361</v>
+        <v>6820443</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,7 +1160,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128601907</v>
+        <v>128601916</v>
       </c>
       <c r="B7" t="n">
         <v>79124</v>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>446217</v>
+        <v>446136</v>
       </c>
       <c r="R7" t="n">
-        <v>6820443</v>
+        <v>6820361</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1750,10 +1750,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128601881</v>
+        <v>128601862</v>
       </c>
       <c r="B13" t="n">
-        <v>79124</v>
+        <v>57717</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1761,34 +1761,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>446035</v>
+        <v>446307</v>
       </c>
       <c r="R13" t="n">
-        <v>6820374</v>
+        <v>6820425</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1847,7 +1855,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128601914</v>
+        <v>128601881</v>
       </c>
       <c r="B14" t="n">
         <v>79124</v>
@@ -1882,10 +1890,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>446152</v>
+        <v>446035</v>
       </c>
       <c r="R14" t="n">
-        <v>6820406</v>
+        <v>6820374</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1944,10 +1952,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128601862</v>
+        <v>128601914</v>
       </c>
       <c r="B15" t="n">
-        <v>57717</v>
+        <v>79124</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1955,42 +1963,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>446307</v>
+        <v>446152</v>
       </c>
       <c r="R15" t="n">
-        <v>6820425</v>
+        <v>6820406</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2635,7 +2635,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128601918</v>
+        <v>128601911</v>
       </c>
       <c r="B22" t="n">
         <v>79124</v>
@@ -2670,10 +2670,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>446114</v>
+        <v>446097</v>
       </c>
       <c r="R22" t="n">
-        <v>6820373</v>
+        <v>6820410</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2732,7 +2732,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128601911</v>
+        <v>128601918</v>
       </c>
       <c r="B23" t="n">
         <v>79124</v>
@@ -2767,10 +2767,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>446097</v>
+        <v>446114</v>
       </c>
       <c r="R23" t="n">
-        <v>6820410</v>
+        <v>6820373</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3225,45 +3225,53 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128601871</v>
+        <v>128601866</v>
       </c>
       <c r="B28" t="n">
-        <v>97507</v>
+        <v>57717</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>446191</v>
+        <v>446314</v>
       </c>
       <c r="R28" t="n">
-        <v>6820410</v>
+        <v>6820495</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3322,53 +3330,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128601866</v>
+        <v>128601871</v>
       </c>
       <c r="B29" t="n">
-        <v>57717</v>
+        <v>97507</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>446314</v>
+        <v>446191</v>
       </c>
       <c r="R29" t="n">
-        <v>6820495</v>
+        <v>6820410</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3815,7 +3815,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128601902</v>
+        <v>128601877</v>
       </c>
       <c r="B34" t="n">
         <v>79124</v>
@@ -3850,10 +3850,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>446302</v>
+        <v>446053</v>
       </c>
       <c r="R34" t="n">
-        <v>6820462</v>
+        <v>6820362</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4009,7 +4009,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128601877</v>
+        <v>128601902</v>
       </c>
       <c r="B36" t="n">
         <v>79124</v>
@@ -4044,10 +4044,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>446053</v>
+        <v>446302</v>
       </c>
       <c r="R36" t="n">
-        <v>6820362</v>
+        <v>6820462</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4106,7 +4106,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128601879</v>
+        <v>128601910</v>
       </c>
       <c r="B37" t="n">
         <v>79124</v>
@@ -4141,10 +4141,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>446049</v>
+        <v>446128</v>
       </c>
       <c r="R37" t="n">
-        <v>6820350</v>
+        <v>6820421</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4203,7 +4203,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128601910</v>
+        <v>128601879</v>
       </c>
       <c r="B38" t="n">
         <v>79124</v>
@@ -4238,10 +4238,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>446128</v>
+        <v>446049</v>
       </c>
       <c r="R38" t="n">
-        <v>6820421</v>
+        <v>6820350</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>

--- a/artfynd/A 37730-2023 artfynd.xlsx
+++ b/artfynd/A 37730-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128601913</v>
       </c>
       <c r="B2" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128601906</v>
+        <v>128601912</v>
       </c>
       <c r="B3" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446239</v>
+        <v>446116</v>
       </c>
       <c r="R3" t="n">
-        <v>6820451</v>
+        <v>6820405</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128601912</v>
+        <v>128601906</v>
       </c>
       <c r="B4" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>446116</v>
+        <v>446239</v>
       </c>
       <c r="R4" t="n">
-        <v>6820405</v>
+        <v>6820451</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128601904</v>
+        <v>128601916</v>
       </c>
       <c r="B5" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>446296</v>
+        <v>446136</v>
       </c>
       <c r="R5" t="n">
-        <v>6820423</v>
+        <v>6820361</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128601907</v>
+        <v>128601904</v>
       </c>
       <c r="B6" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>446217</v>
+        <v>446296</v>
       </c>
       <c r="R6" t="n">
-        <v>6820443</v>
+        <v>6820423</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128601916</v>
+        <v>128601907</v>
       </c>
       <c r="B7" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>446136</v>
+        <v>446217</v>
       </c>
       <c r="R7" t="n">
-        <v>6820361</v>
+        <v>6820443</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1260,7 +1260,7 @@
         <v>128601908</v>
       </c>
       <c r="B8" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128601897</v>
+        <v>128601865</v>
       </c>
       <c r="B9" t="n">
-        <v>79124</v>
+        <v>57720</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,34 +1365,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>446488</v>
+        <v>446361</v>
       </c>
       <c r="R9" t="n">
-        <v>6820524</v>
+        <v>6820513</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,10 +1459,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128601865</v>
+        <v>128601897</v>
       </c>
       <c r="B10" t="n">
-        <v>57717</v>
+        <v>79029</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,42 +1470,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>446361</v>
+        <v>446488</v>
       </c>
       <c r="R10" t="n">
-        <v>6820513</v>
+        <v>6820524</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1559,7 +1559,7 @@
         <v>128601915</v>
       </c>
       <c r="B11" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>128601880</v>
       </c>
       <c r="B12" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1750,53 +1750,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128601862</v>
+        <v>128601870</v>
       </c>
       <c r="B13" t="n">
-        <v>57717</v>
+        <v>97514</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>446307</v>
+        <v>446224</v>
       </c>
       <c r="R13" t="n">
-        <v>6820425</v>
+        <v>6820433</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1858,7 +1850,7 @@
         <v>128601881</v>
       </c>
       <c r="B14" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1955,7 +1947,7 @@
         <v>128601914</v>
       </c>
       <c r="B15" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2049,45 +2041,53 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128601870</v>
+        <v>128601862</v>
       </c>
       <c r="B16" t="n">
-        <v>97507</v>
+        <v>57720</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>446224</v>
+        <v>446307</v>
       </c>
       <c r="R16" t="n">
-        <v>6820433</v>
+        <v>6820425</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2149,7 +2149,7 @@
         <v>128601921</v>
       </c>
       <c r="B17" t="n">
-        <v>91010</v>
+        <v>91015</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>128601919</v>
       </c>
       <c r="B18" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
         <v>128601909</v>
       </c>
       <c r="B19" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>128601864</v>
       </c>
       <c r="B20" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>128601873</v>
       </c>
       <c r="B21" t="n">
-        <v>78882</v>
+        <v>78787</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2635,10 +2635,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128601911</v>
+        <v>128601918</v>
       </c>
       <c r="B22" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2670,10 +2670,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>446097</v>
+        <v>446114</v>
       </c>
       <c r="R22" t="n">
-        <v>6820410</v>
+        <v>6820373</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2732,10 +2732,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128601918</v>
+        <v>128601911</v>
       </c>
       <c r="B23" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2767,10 +2767,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>446114</v>
+        <v>446097</v>
       </c>
       <c r="R23" t="n">
-        <v>6820373</v>
+        <v>6820410</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2832,7 +2832,7 @@
         <v>128601869</v>
       </c>
       <c r="B24" t="n">
-        <v>97507</v>
+        <v>97514</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2926,10 +2926,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128601882</v>
+        <v>128601876</v>
       </c>
       <c r="B25" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2961,10 +2961,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>446143</v>
+        <v>446231</v>
       </c>
       <c r="R25" t="n">
-        <v>6820358</v>
+        <v>6820457</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3023,10 +3023,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128601876</v>
+        <v>128601882</v>
       </c>
       <c r="B26" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>446231</v>
+        <v>446143</v>
       </c>
       <c r="R26" t="n">
-        <v>6820457</v>
+        <v>6820358</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3123,7 +3123,7 @@
         <v>128601863</v>
       </c>
       <c r="B27" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3225,53 +3225,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128601866</v>
+        <v>128601871</v>
       </c>
       <c r="B28" t="n">
-        <v>57717</v>
+        <v>97514</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>446314</v>
+        <v>446191</v>
       </c>
       <c r="R28" t="n">
-        <v>6820495</v>
+        <v>6820410</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3330,45 +3322,53 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128601871</v>
+        <v>128601866</v>
       </c>
       <c r="B29" t="n">
-        <v>97507</v>
+        <v>57720</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>446191</v>
+        <v>446314</v>
       </c>
       <c r="R29" t="n">
-        <v>6820410</v>
+        <v>6820495</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3430,7 +3430,7 @@
         <v>128601917</v>
       </c>
       <c r="B30" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>128601903</v>
       </c>
       <c r="B31" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3624,7 +3624,7 @@
         <v>128601900</v>
       </c>
       <c r="B32" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3721,7 +3721,7 @@
         <v>128601905</v>
       </c>
       <c r="B33" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3815,10 +3815,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128601877</v>
+        <v>128601902</v>
       </c>
       <c r="B34" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3850,10 +3850,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>446053</v>
+        <v>446302</v>
       </c>
       <c r="R34" t="n">
-        <v>6820362</v>
+        <v>6820462</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3912,10 +3912,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128601899</v>
+        <v>128601877</v>
       </c>
       <c r="B35" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3947,10 +3947,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>446477</v>
+        <v>446053</v>
       </c>
       <c r="R35" t="n">
-        <v>6820530</v>
+        <v>6820362</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4009,10 +4009,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128601902</v>
+        <v>128601899</v>
       </c>
       <c r="B36" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4044,10 +4044,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>446302</v>
+        <v>446477</v>
       </c>
       <c r="R36" t="n">
-        <v>6820462</v>
+        <v>6820530</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4106,10 +4106,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128601910</v>
+        <v>128601879</v>
       </c>
       <c r="B37" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4141,10 +4141,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>446128</v>
+        <v>446049</v>
       </c>
       <c r="R37" t="n">
-        <v>6820421</v>
+        <v>6820350</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4203,10 +4203,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128601879</v>
+        <v>128601910</v>
       </c>
       <c r="B38" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4238,10 +4238,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>446049</v>
+        <v>446128</v>
       </c>
       <c r="R38" t="n">
-        <v>6820350</v>
+        <v>6820421</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>

--- a/artfynd/A 37730-2023 artfynd.xlsx
+++ b/artfynd/A 37730-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128601913</v>
       </c>
       <c r="B2" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128601906</v>
+        <v>128601912</v>
       </c>
       <c r="B3" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446239</v>
+        <v>446116</v>
       </c>
       <c r="R3" t="n">
-        <v>6820451</v>
+        <v>6820405</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128601912</v>
+        <v>128601906</v>
       </c>
       <c r="B4" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>446116</v>
+        <v>446239</v>
       </c>
       <c r="R4" t="n">
-        <v>6820405</v>
+        <v>6820451</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
         <v>128601904</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128601907</v>
+        <v>128601916</v>
       </c>
       <c r="B6" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>446217</v>
+        <v>446136</v>
       </c>
       <c r="R6" t="n">
-        <v>6820443</v>
+        <v>6820361</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128601916</v>
+        <v>128601907</v>
       </c>
       <c r="B7" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>446136</v>
+        <v>446217</v>
       </c>
       <c r="R7" t="n">
-        <v>6820361</v>
+        <v>6820443</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1260,7 +1260,7 @@
         <v>128601908</v>
       </c>
       <c r="B8" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128601865</v>
+        <v>128601897</v>
       </c>
       <c r="B9" t="n">
-        <v>57720</v>
+        <v>79034</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,42 +1365,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>446361</v>
+        <v>446488</v>
       </c>
       <c r="R9" t="n">
-        <v>6820513</v>
+        <v>6820524</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1459,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128601897</v>
+        <v>128601865</v>
       </c>
       <c r="B10" t="n">
-        <v>79029</v>
+        <v>57720</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1470,34 +1462,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>446488</v>
+        <v>446361</v>
       </c>
       <c r="R10" t="n">
-        <v>6820524</v>
+        <v>6820513</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1559,7 +1559,7 @@
         <v>128601915</v>
       </c>
       <c r="B11" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>128601880</v>
       </c>
       <c r="B12" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1750,10 +1750,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128601862</v>
+        <v>128601881</v>
       </c>
       <c r="B13" t="n">
-        <v>57720</v>
+        <v>79034</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1761,42 +1761,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>446307</v>
+        <v>446035</v>
       </c>
       <c r="R13" t="n">
-        <v>6820425</v>
+        <v>6820374</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1855,32 +1847,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128601870</v>
+        <v>128601914</v>
       </c>
       <c r="B14" t="n">
-        <v>97517</v>
+        <v>79034</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1890,10 +1882,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>446224</v>
+        <v>446152</v>
       </c>
       <c r="R14" t="n">
-        <v>6820433</v>
+        <v>6820406</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1952,10 +1944,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128601881</v>
+        <v>128601862</v>
       </c>
       <c r="B15" t="n">
-        <v>79029</v>
+        <v>57720</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1963,34 +1955,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>446035</v>
+        <v>446307</v>
       </c>
       <c r="R15" t="n">
-        <v>6820374</v>
+        <v>6820425</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2049,32 +2049,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128601914</v>
+        <v>128601870</v>
       </c>
       <c r="B16" t="n">
-        <v>79029</v>
+        <v>97522</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2084,10 +2084,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>446152</v>
+        <v>446224</v>
       </c>
       <c r="R16" t="n">
-        <v>6820406</v>
+        <v>6820433</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2149,7 +2149,7 @@
         <v>128601921</v>
       </c>
       <c r="B17" t="n">
-        <v>91017</v>
+        <v>91022</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>128601919</v>
       </c>
       <c r="B18" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2344,10 +2344,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128601864</v>
+        <v>128601909</v>
       </c>
       <c r="B19" t="n">
-        <v>57720</v>
+        <v>79034</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2355,21 +2355,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2379,10 +2379,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>446223</v>
+        <v>446185</v>
       </c>
       <c r="R19" t="n">
-        <v>6820431</v>
+        <v>6820420</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2441,10 +2441,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128601909</v>
+        <v>128601864</v>
       </c>
       <c r="B20" t="n">
-        <v>79029</v>
+        <v>57720</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2452,21 +2452,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2476,10 +2476,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>446185</v>
+        <v>446223</v>
       </c>
       <c r="R20" t="n">
-        <v>6820420</v>
+        <v>6820431</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2541,7 +2541,7 @@
         <v>128601873</v>
       </c>
       <c r="B21" t="n">
-        <v>78787</v>
+        <v>78792</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2635,32 +2635,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128601869</v>
+        <v>128601911</v>
       </c>
       <c r="B22" t="n">
-        <v>97517</v>
+        <v>79034</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2670,10 +2670,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>446357</v>
+        <v>446097</v>
       </c>
       <c r="R22" t="n">
-        <v>6820512</v>
+        <v>6820410</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2732,10 +2732,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128601911</v>
+        <v>128601918</v>
       </c>
       <c r="B23" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2767,10 +2767,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>446097</v>
+        <v>446114</v>
       </c>
       <c r="R23" t="n">
-        <v>6820410</v>
+        <v>6820373</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2829,32 +2829,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128601918</v>
+        <v>128601869</v>
       </c>
       <c r="B24" t="n">
-        <v>79029</v>
+        <v>97522</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2864,10 +2864,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>446114</v>
+        <v>446357</v>
       </c>
       <c r="R24" t="n">
-        <v>6820373</v>
+        <v>6820512</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2926,10 +2926,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128601863</v>
+        <v>128601882</v>
       </c>
       <c r="B25" t="n">
-        <v>57720</v>
+        <v>79034</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2937,42 +2937,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>446183</v>
+        <v>446143</v>
       </c>
       <c r="R25" t="n">
-        <v>6820440</v>
+        <v>6820358</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3031,10 +3023,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128601882</v>
+        <v>128601876</v>
       </c>
       <c r="B26" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3066,10 +3058,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>446143</v>
+        <v>446231</v>
       </c>
       <c r="R26" t="n">
-        <v>6820358</v>
+        <v>6820457</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3128,10 +3120,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128601876</v>
+        <v>128601863</v>
       </c>
       <c r="B27" t="n">
-        <v>79029</v>
+        <v>57720</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3139,34 +3131,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>446231</v>
+        <v>446183</v>
       </c>
       <c r="R27" t="n">
-        <v>6820457</v>
+        <v>6820440</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3225,53 +3225,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128601866</v>
+        <v>128601871</v>
       </c>
       <c r="B28" t="n">
-        <v>57720</v>
+        <v>97522</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>446314</v>
+        <v>446191</v>
       </c>
       <c r="R28" t="n">
-        <v>6820495</v>
+        <v>6820410</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3330,45 +3322,53 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128601871</v>
+        <v>128601866</v>
       </c>
       <c r="B29" t="n">
-        <v>97517</v>
+        <v>57720</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>446191</v>
+        <v>446314</v>
       </c>
       <c r="R29" t="n">
-        <v>6820410</v>
+        <v>6820495</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3430,7 +3430,7 @@
         <v>128601917</v>
       </c>
       <c r="B30" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>128601903</v>
       </c>
       <c r="B31" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3624,7 +3624,7 @@
         <v>128601900</v>
       </c>
       <c r="B32" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3721,7 +3721,7 @@
         <v>128601905</v>
       </c>
       <c r="B33" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3815,10 +3815,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128601877</v>
+        <v>128601902</v>
       </c>
       <c r="B34" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3850,10 +3850,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>446053</v>
+        <v>446302</v>
       </c>
       <c r="R34" t="n">
-        <v>6820362</v>
+        <v>6820462</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3915,7 +3915,7 @@
         <v>128601899</v>
       </c>
       <c r="B35" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4009,10 +4009,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128601902</v>
+        <v>128601877</v>
       </c>
       <c r="B36" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4044,10 +4044,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>446302</v>
+        <v>446053</v>
       </c>
       <c r="R36" t="n">
-        <v>6820462</v>
+        <v>6820362</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4106,10 +4106,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128601910</v>
+        <v>128601879</v>
       </c>
       <c r="B37" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4141,10 +4141,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>446128</v>
+        <v>446049</v>
       </c>
       <c r="R37" t="n">
-        <v>6820421</v>
+        <v>6820350</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4203,10 +4203,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128601879</v>
+        <v>128601910</v>
       </c>
       <c r="B38" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4238,10 +4238,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>446049</v>
+        <v>446128</v>
       </c>
       <c r="R38" t="n">
-        <v>6820350</v>
+        <v>6820421</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>

--- a/artfynd/A 37730-2023 artfynd.xlsx
+++ b/artfynd/A 37730-2023 artfynd.xlsx
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128601897</v>
+        <v>128601865</v>
       </c>
       <c r="B9" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,34 +1365,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>446488</v>
+        <v>446361</v>
       </c>
       <c r="R9" t="n">
-        <v>6820524</v>
+        <v>6820513</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,10 +1459,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128601865</v>
+        <v>128601897</v>
       </c>
       <c r="B10" t="n">
-        <v>57720</v>
+        <v>79034</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,42 +1470,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>446361</v>
+        <v>446488</v>
       </c>
       <c r="R10" t="n">
-        <v>6820513</v>
+        <v>6820524</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1944,53 +1944,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128601862</v>
+        <v>128601870</v>
       </c>
       <c r="B15" t="n">
-        <v>57720</v>
+        <v>97522</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>446307</v>
+        <v>446224</v>
       </c>
       <c r="R15" t="n">
-        <v>6820425</v>
+        <v>6820433</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2049,45 +2041,53 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128601870</v>
+        <v>128601862</v>
       </c>
       <c r="B16" t="n">
-        <v>97522</v>
+        <v>57720</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>446224</v>
+        <v>446307</v>
       </c>
       <c r="R16" t="n">
-        <v>6820433</v>
+        <v>6820425</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -3225,45 +3225,53 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128601871</v>
+        <v>128601866</v>
       </c>
       <c r="B28" t="n">
-        <v>97522</v>
+        <v>57720</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>446191</v>
+        <v>446314</v>
       </c>
       <c r="R28" t="n">
-        <v>6820410</v>
+        <v>6820495</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3322,53 +3330,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128601866</v>
+        <v>128601871</v>
       </c>
       <c r="B29" t="n">
-        <v>57720</v>
+        <v>97522</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>446314</v>
+        <v>446191</v>
       </c>
       <c r="R29" t="n">
-        <v>6820495</v>
+        <v>6820410</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>

--- a/artfynd/A 37730-2023 artfynd.xlsx
+++ b/artfynd/A 37730-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128601913</v>
       </c>
       <c r="B2" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128601912</v>
       </c>
       <c r="B3" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128601906</v>
       </c>
       <c r="B4" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128601904</v>
+        <v>128601916</v>
       </c>
       <c r="B5" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>446296</v>
+        <v>446136</v>
       </c>
       <c r="R5" t="n">
-        <v>6820423</v>
+        <v>6820361</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128601916</v>
+        <v>128601907</v>
       </c>
       <c r="B6" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>446136</v>
+        <v>446217</v>
       </c>
       <c r="R6" t="n">
-        <v>6820361</v>
+        <v>6820443</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128601907</v>
+        <v>128601904</v>
       </c>
       <c r="B7" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>446217</v>
+        <v>446296</v>
       </c>
       <c r="R7" t="n">
-        <v>6820443</v>
+        <v>6820423</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1260,7 +1260,7 @@
         <v>128601908</v>
       </c>
       <c r="B8" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128601865</v>
+        <v>128601897</v>
       </c>
       <c r="B9" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,42 +1365,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>446361</v>
+        <v>446488</v>
       </c>
       <c r="R9" t="n">
-        <v>6820513</v>
+        <v>6820524</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1459,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128601897</v>
+        <v>128601865</v>
       </c>
       <c r="B10" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1470,34 +1462,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>446488</v>
+        <v>446361</v>
       </c>
       <c r="R10" t="n">
-        <v>6820524</v>
+        <v>6820513</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1559,7 +1559,7 @@
         <v>128601915</v>
       </c>
       <c r="B11" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>128601880</v>
       </c>
       <c r="B12" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1750,10 +1750,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128601881</v>
+        <v>128601862</v>
       </c>
       <c r="B13" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1761,34 +1761,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>446035</v>
+        <v>446307</v>
       </c>
       <c r="R13" t="n">
-        <v>6820374</v>
+        <v>6820425</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1847,10 +1855,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128601914</v>
+        <v>128601881</v>
       </c>
       <c r="B14" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1882,10 +1890,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>446152</v>
+        <v>446035</v>
       </c>
       <c r="R14" t="n">
-        <v>6820406</v>
+        <v>6820374</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1944,32 +1952,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128601870</v>
+        <v>128601914</v>
       </c>
       <c r="B15" t="n">
-        <v>97522</v>
+        <v>79035</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1979,10 +1987,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>446224</v>
+        <v>446152</v>
       </c>
       <c r="R15" t="n">
-        <v>6820433</v>
+        <v>6820406</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2041,53 +2049,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128601862</v>
+        <v>128601870</v>
       </c>
       <c r="B16" t="n">
-        <v>57720</v>
+        <v>97530</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>446307</v>
+        <v>446224</v>
       </c>
       <c r="R16" t="n">
-        <v>6820425</v>
+        <v>6820433</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2149,7 +2149,7 @@
         <v>128601921</v>
       </c>
       <c r="B17" t="n">
-        <v>91022</v>
+        <v>91028</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>128601919</v>
       </c>
       <c r="B18" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
         <v>128601909</v>
       </c>
       <c r="B19" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>128601873</v>
       </c>
       <c r="B21" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2635,32 +2635,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128601911</v>
+        <v>128601869</v>
       </c>
       <c r="B22" t="n">
-        <v>79034</v>
+        <v>97530</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2670,10 +2670,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>446097</v>
+        <v>446357</v>
       </c>
       <c r="R22" t="n">
-        <v>6820410</v>
+        <v>6820512</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2732,10 +2732,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128601918</v>
+        <v>128601911</v>
       </c>
       <c r="B23" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2767,10 +2767,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>446114</v>
+        <v>446097</v>
       </c>
       <c r="R23" t="n">
-        <v>6820373</v>
+        <v>6820410</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2829,32 +2829,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128601869</v>
+        <v>128601918</v>
       </c>
       <c r="B24" t="n">
-        <v>97522</v>
+        <v>79035</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2864,10 +2864,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>446357</v>
+        <v>446114</v>
       </c>
       <c r="R24" t="n">
-        <v>6820512</v>
+        <v>6820373</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2929,7 +2929,7 @@
         <v>128601882</v>
       </c>
       <c r="B25" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         <v>128601876</v>
       </c>
       <c r="B26" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>128601871</v>
       </c>
       <c r="B29" t="n">
-        <v>97522</v>
+        <v>97530</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>128601917</v>
       </c>
       <c r="B30" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>128601903</v>
       </c>
       <c r="B31" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3624,7 +3624,7 @@
         <v>128601900</v>
       </c>
       <c r="B32" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3721,7 +3721,7 @@
         <v>128601905</v>
       </c>
       <c r="B33" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3818,7 +3818,7 @@
         <v>128601902</v>
       </c>
       <c r="B34" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3915,7 +3915,7 @@
         <v>128601899</v>
       </c>
       <c r="B35" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4012,7 +4012,7 @@
         <v>128601877</v>
       </c>
       <c r="B36" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4109,7 +4109,7 @@
         <v>128601879</v>
       </c>
       <c r="B37" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
         <v>128601910</v>
       </c>
       <c r="B38" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 37730-2023 artfynd.xlsx
+++ b/artfynd/A 37730-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AY57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128601912</v>
+        <v>128601906</v>
       </c>
       <c r="B3" t="n">
         <v>79035</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446116</v>
+        <v>446239</v>
       </c>
       <c r="R3" t="n">
-        <v>6820405</v>
+        <v>6820451</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128601906</v>
+        <v>128601912</v>
       </c>
       <c r="B4" t="n">
         <v>79035</v>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>446239</v>
+        <v>446116</v>
       </c>
       <c r="R4" t="n">
-        <v>6820451</v>
+        <v>6820405</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128601897</v>
+        <v>128601865</v>
       </c>
       <c r="B9" t="n">
-        <v>79035</v>
+        <v>57720</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,34 +1365,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>446488</v>
+        <v>446361</v>
       </c>
       <c r="R9" t="n">
-        <v>6820524</v>
+        <v>6820513</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,10 +1459,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128601865</v>
+        <v>128601897</v>
       </c>
       <c r="B10" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,42 +1470,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>446361</v>
+        <v>446488</v>
       </c>
       <c r="R10" t="n">
-        <v>6820513</v>
+        <v>6820524</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -3718,7 +3718,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128601905</v>
+        <v>128601877</v>
       </c>
       <c r="B33" t="n">
         <v>79035</v>
@@ -3753,10 +3753,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>446304</v>
+        <v>446053</v>
       </c>
       <c r="R33" t="n">
-        <v>6820419</v>
+        <v>6820362</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3815,7 +3815,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128601902</v>
+        <v>128601905</v>
       </c>
       <c r="B34" t="n">
         <v>79035</v>
@@ -3850,10 +3850,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>446302</v>
+        <v>446304</v>
       </c>
       <c r="R34" t="n">
-        <v>6820462</v>
+        <v>6820419</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3912,7 +3912,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128601899</v>
+        <v>128601902</v>
       </c>
       <c r="B35" t="n">
         <v>79035</v>
@@ -3947,10 +3947,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>446477</v>
+        <v>446302</v>
       </c>
       <c r="R35" t="n">
-        <v>6820530</v>
+        <v>6820462</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4009,7 +4009,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128601877</v>
+        <v>128601899</v>
       </c>
       <c r="B36" t="n">
         <v>79035</v>
@@ -4044,10 +4044,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>446053</v>
+        <v>446477</v>
       </c>
       <c r="R36" t="n">
-        <v>6820362</v>
+        <v>6820530</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4298,6 +4298,2095 @@
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>129129057</v>
+      </c>
+      <c r="B39" t="n">
+        <v>92819</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Balser, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>446139</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6820379</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>129128711</v>
+      </c>
+      <c r="B40" t="n">
+        <v>98659</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Balser, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>446080</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6820372</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>129128615</v>
+      </c>
+      <c r="B41" t="n">
+        <v>79067</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>185</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Balser, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>446133</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6820337</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>129128718</v>
+      </c>
+      <c r="B42" t="n">
+        <v>98659</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Balser, Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>446097</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6820373</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>129128729</v>
+      </c>
+      <c r="B43" t="n">
+        <v>98659</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Balser, Dlr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>446069</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6820383</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>129128606</v>
+      </c>
+      <c r="B44" t="n">
+        <v>83011</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Balser, Dlr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>446023</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6820366</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>129129028</v>
+      </c>
+      <c r="B45" t="n">
+        <v>79035</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Balser, Dlr</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>446053</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6820359</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>129128684</v>
+      </c>
+      <c r="B46" t="n">
+        <v>80176</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Balser, Dlr</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>446038</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6820345</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>129129069</v>
+      </c>
+      <c r="B47" t="n">
+        <v>57723</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Balser, Dlr</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>446053</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6820359</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>129128609</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79067</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>185</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Balser, Dlr</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>446159</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6820355</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>129129042</v>
+      </c>
+      <c r="B49" t="n">
+        <v>79035</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Balser, Dlr</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>446133</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6820336</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>129128710</v>
+      </c>
+      <c r="B50" t="n">
+        <v>98659</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Balser, Dlr</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>446091</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6820378</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>129129026</v>
+      </c>
+      <c r="B51" t="n">
+        <v>79035</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Balser, Dlr</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>446012</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6820359</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>129129068</v>
+      </c>
+      <c r="B52" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Balser, Dlr</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>446072</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6820368</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>129129029</v>
+      </c>
+      <c r="B53" t="n">
+        <v>79035</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Balser, Dlr</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>446072</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6820367</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>129128639</v>
+      </c>
+      <c r="B54" t="n">
+        <v>57720</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Balser, Dlr</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>446125</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6820377</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>129129056</v>
+      </c>
+      <c r="B55" t="n">
+        <v>92819</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Balser, Dlr</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>446126</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6820377</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>129129027</v>
+      </c>
+      <c r="B56" t="n">
+        <v>79035</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Balser, Dlr</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>446038</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6820345</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>129129030</v>
+      </c>
+      <c r="B57" t="n">
+        <v>79035</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Balser, Dlr</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>446128</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6820377</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37730-2023 artfynd.xlsx
+++ b/artfynd/A 37730-2023 artfynd.xlsx
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128601906</v>
+        <v>128601912</v>
       </c>
       <c r="B3" t="n">
         <v>79035</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446239</v>
+        <v>446116</v>
       </c>
       <c r="R3" t="n">
-        <v>6820451</v>
+        <v>6820405</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128601912</v>
+        <v>128601906</v>
       </c>
       <c r="B4" t="n">
         <v>79035</v>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>446116</v>
+        <v>446239</v>
       </c>
       <c r="R4" t="n">
-        <v>6820405</v>
+        <v>6820451</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,7 +966,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128601916</v>
+        <v>128601904</v>
       </c>
       <c r="B5" t="n">
         <v>79035</v>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>446136</v>
+        <v>446296</v>
       </c>
       <c r="R5" t="n">
-        <v>6820361</v>
+        <v>6820423</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,7 +1063,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128601907</v>
+        <v>128601916</v>
       </c>
       <c r="B6" t="n">
         <v>79035</v>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>446217</v>
+        <v>446136</v>
       </c>
       <c r="R6" t="n">
-        <v>6820443</v>
+        <v>6820361</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,7 +1160,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128601904</v>
+        <v>128601907</v>
       </c>
       <c r="B7" t="n">
         <v>79035</v>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>446296</v>
+        <v>446217</v>
       </c>
       <c r="R7" t="n">
-        <v>6820423</v>
+        <v>6820443</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128601865</v>
+        <v>128601897</v>
       </c>
       <c r="B9" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,42 +1365,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>446361</v>
+        <v>446488</v>
       </c>
       <c r="R9" t="n">
-        <v>6820513</v>
+        <v>6820524</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1459,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128601897</v>
+        <v>128601865</v>
       </c>
       <c r="B10" t="n">
-        <v>79035</v>
+        <v>57720</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1470,34 +1462,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>446488</v>
+        <v>446361</v>
       </c>
       <c r="R10" t="n">
-        <v>6820524</v>
+        <v>6820513</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1750,53 +1750,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128601862</v>
+        <v>128601870</v>
       </c>
       <c r="B13" t="n">
-        <v>57720</v>
+        <v>97530</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>446307</v>
+        <v>446224</v>
       </c>
       <c r="R13" t="n">
-        <v>6820425</v>
+        <v>6820433</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1855,10 +1847,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128601881</v>
+        <v>128601862</v>
       </c>
       <c r="B14" t="n">
-        <v>79035</v>
+        <v>57720</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1866,34 +1858,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>446035</v>
+        <v>446307</v>
       </c>
       <c r="R14" t="n">
-        <v>6820374</v>
+        <v>6820425</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1952,7 +1952,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128601914</v>
+        <v>128601881</v>
       </c>
       <c r="B15" t="n">
         <v>79035</v>
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>446152</v>
+        <v>446035</v>
       </c>
       <c r="R15" t="n">
-        <v>6820406</v>
+        <v>6820374</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2049,32 +2049,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128601870</v>
+        <v>128601914</v>
       </c>
       <c r="B16" t="n">
-        <v>97530</v>
+        <v>79035</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2084,10 +2084,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>446224</v>
+        <v>446152</v>
       </c>
       <c r="R16" t="n">
-        <v>6820433</v>
+        <v>6820406</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -3225,53 +3225,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128601866</v>
+        <v>128601871</v>
       </c>
       <c r="B28" t="n">
-        <v>57720</v>
+        <v>97530</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>446314</v>
+        <v>446191</v>
       </c>
       <c r="R28" t="n">
-        <v>6820495</v>
+        <v>6820410</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3330,45 +3322,53 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128601871</v>
+        <v>128601866</v>
       </c>
       <c r="B29" t="n">
-        <v>97530</v>
+        <v>57720</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>446191</v>
+        <v>446314</v>
       </c>
       <c r="R29" t="n">
-        <v>6820410</v>
+        <v>6820495</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3718,7 +3718,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128601877</v>
+        <v>128601905</v>
       </c>
       <c r="B33" t="n">
         <v>79035</v>
@@ -3753,10 +3753,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>446053</v>
+        <v>446304</v>
       </c>
       <c r="R33" t="n">
-        <v>6820362</v>
+        <v>6820419</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3815,7 +3815,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128601905</v>
+        <v>128601902</v>
       </c>
       <c r="B34" t="n">
         <v>79035</v>
@@ -3850,10 +3850,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>446304</v>
+        <v>446302</v>
       </c>
       <c r="R34" t="n">
-        <v>6820419</v>
+        <v>6820462</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3912,7 +3912,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128601902</v>
+        <v>128601899</v>
       </c>
       <c r="B35" t="n">
         <v>79035</v>
@@ -3947,10 +3947,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>446302</v>
+        <v>446477</v>
       </c>
       <c r="R35" t="n">
-        <v>6820462</v>
+        <v>6820530</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4009,7 +4009,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128601899</v>
+        <v>128601877</v>
       </c>
       <c r="B36" t="n">
         <v>79035</v>
@@ -4044,10 +4044,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>446477</v>
+        <v>446053</v>
       </c>
       <c r="R36" t="n">
-        <v>6820530</v>
+        <v>6820362</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4862,10 +4862,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129128606</v>
+        <v>129129028</v>
       </c>
       <c r="B44" t="n">
-        <v>83011</v>
+        <v>79035</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4873,34 +4873,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>446023</v>
+        <v>446053</v>
       </c>
       <c r="R44" t="n">
-        <v>6820366</v>
+        <v>6820359</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4932,7 +4937,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -4942,7 +4947,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4969,10 +4974,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129129028</v>
+        <v>129128606</v>
       </c>
       <c r="B45" t="n">
-        <v>79035</v>
+        <v>83011</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4980,39 +4985,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>446053</v>
+        <v>446023</v>
       </c>
       <c r="R45" t="n">
-        <v>6820359</v>
+        <v>6820366</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5044,7 +5044,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD45" t="b">

--- a/artfynd/A 37730-2023 artfynd.xlsx
+++ b/artfynd/A 37730-2023 artfynd.xlsx
@@ -5956,32 +5956,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129128639</v>
+        <v>129129056</v>
       </c>
       <c r="B54" t="n">
-        <v>57720</v>
+        <v>92819</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5991,7 +5991,7 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>446125</v>
+        <v>446126</v>
       </c>
       <c r="R54" t="n">
         <v>6820377</v>
@@ -6063,32 +6063,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129129056</v>
+        <v>129128639</v>
       </c>
       <c r="B55" t="n">
-        <v>92819</v>
+        <v>57720</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6098,7 +6098,7 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>446126</v>
+        <v>446125</v>
       </c>
       <c r="R55" t="n">
         <v>6820377</v>

--- a/artfynd/A 37730-2023 artfynd.xlsx
+++ b/artfynd/A 37730-2023 artfynd.xlsx
@@ -4303,7 +4303,7 @@
         <v>129129057</v>
       </c>
       <c r="B39" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4410,7 +4410,7 @@
         <v>129128711</v>
       </c>
       <c r="B40" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4526,7 +4526,7 @@
         <v>129128615</v>
       </c>
       <c r="B41" t="n">
-        <v>79067</v>
+        <v>79071</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4633,7 +4633,7 @@
         <v>129128718</v>
       </c>
       <c r="B42" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         <v>129128729</v>
       </c>
       <c r="B43" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4865,7 +4865,7 @@
         <v>129129028</v>
       </c>
       <c r="B44" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4977,7 +4977,7 @@
         <v>129128606</v>
       </c>
       <c r="B45" t="n">
-        <v>83011</v>
+        <v>83015</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
         <v>129128684</v>
       </c>
       <c r="B46" t="n">
-        <v>80176</v>
+        <v>80180</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5191,7 +5191,7 @@
         <v>129129069</v>
       </c>
       <c r="B47" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
         <v>129128609</v>
       </c>
       <c r="B48" t="n">
-        <v>79067</v>
+        <v>79071</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5407,45 +5407,54 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129129042</v>
+        <v>129128710</v>
       </c>
       <c r="B49" t="n">
-        <v>79035</v>
+        <v>98669</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>446133</v>
+        <v>446091</v>
       </c>
       <c r="R49" t="n">
-        <v>6820336</v>
+        <v>6820378</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5477,7 +5486,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5487,7 +5496,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5514,54 +5523,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129128710</v>
+        <v>129129042</v>
       </c>
       <c r="B50" t="n">
-        <v>98659</v>
+        <v>79039</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>446091</v>
+        <v>446133</v>
       </c>
       <c r="R50" t="n">
-        <v>6820378</v>
+        <v>6820336</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5593,7 +5593,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5603,7 +5603,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5633,7 +5633,7 @@
         <v>129129026</v>
       </c>
       <c r="B51" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5852,7 +5852,7 @@
         <v>129129029</v>
       </c>
       <c r="B53" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5959,7 +5959,7 @@
         <v>129129056</v>
       </c>
       <c r="B54" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6066,7 +6066,7 @@
         <v>129128639</v>
       </c>
       <c r="B55" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6170,10 +6170,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129129027</v>
+        <v>129129030</v>
       </c>
       <c r="B56" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6199,21 +6199,16 @@
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>446038</v>
+        <v>446128</v>
       </c>
       <c r="R56" t="n">
-        <v>6820345</v>
+        <v>6820377</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6245,7 +6240,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6255,7 +6250,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6282,10 +6277,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129129030</v>
+        <v>129129027</v>
       </c>
       <c r="B57" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6311,16 +6306,21 @@
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>446128</v>
+        <v>446038</v>
       </c>
       <c r="R57" t="n">
-        <v>6820377</v>
+        <v>6820345</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6362,7 +6362,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD57" t="b">

--- a/artfynd/A 37730-2023 artfynd.xlsx
+++ b/artfynd/A 37730-2023 artfynd.xlsx
@@ -5407,54 +5407,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129128710</v>
+        <v>129129042</v>
       </c>
       <c r="B49" t="n">
-        <v>98669</v>
+        <v>79039</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>446091</v>
+        <v>446133</v>
       </c>
       <c r="R49" t="n">
-        <v>6820378</v>
+        <v>6820336</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5486,7 +5477,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5496,7 +5487,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5523,45 +5514,54 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129129042</v>
+        <v>129128710</v>
       </c>
       <c r="B50" t="n">
-        <v>79039</v>
+        <v>98669</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>446133</v>
+        <v>446091</v>
       </c>
       <c r="R50" t="n">
-        <v>6820336</v>
+        <v>6820378</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5593,7 +5593,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5603,7 +5603,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD50" t="b">

--- a/artfynd/A 37730-2023 artfynd.xlsx
+++ b/artfynd/A 37730-2023 artfynd.xlsx
@@ -4303,7 +4303,7 @@
         <v>129129057</v>
       </c>
       <c r="B39" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4410,7 +4410,7 @@
         <v>129128711</v>
       </c>
       <c r="B40" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4633,7 +4633,7 @@
         <v>129128718</v>
       </c>
       <c r="B42" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         <v>129128729</v>
       </c>
       <c r="B43" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4862,10 +4862,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129129028</v>
+        <v>129128606</v>
       </c>
       <c r="B44" t="n">
-        <v>79039</v>
+        <v>83005</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4873,39 +4873,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>446053</v>
+        <v>446023</v>
       </c>
       <c r="R44" t="n">
-        <v>6820359</v>
+        <v>6820366</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4937,7 +4932,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -4947,7 +4942,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4974,10 +4969,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129128606</v>
+        <v>129129028</v>
       </c>
       <c r="B45" t="n">
-        <v>83015</v>
+        <v>79039</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4985,34 +4980,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>446023</v>
+        <v>446053</v>
       </c>
       <c r="R45" t="n">
-        <v>6820366</v>
+        <v>6820359</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5044,7 +5044,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5407,45 +5407,54 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129129042</v>
+        <v>129128710</v>
       </c>
       <c r="B49" t="n">
-        <v>79039</v>
+        <v>98676</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>446133</v>
+        <v>446091</v>
       </c>
       <c r="R49" t="n">
-        <v>6820336</v>
+        <v>6820378</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5477,7 +5486,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5487,7 +5496,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5514,54 +5523,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129128710</v>
+        <v>129129042</v>
       </c>
       <c r="B50" t="n">
-        <v>98669</v>
+        <v>79039</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>446091</v>
+        <v>446133</v>
       </c>
       <c r="R50" t="n">
-        <v>6820378</v>
+        <v>6820336</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5593,7 +5593,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5603,7 +5603,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5959,7 +5959,7 @@
         <v>129129056</v>
       </c>
       <c r="B54" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6170,7 +6170,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129129030</v>
+        <v>129129027</v>
       </c>
       <c r="B56" t="n">
         <v>79039</v>
@@ -6199,16 +6199,21 @@
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>446128</v>
+        <v>446038</v>
       </c>
       <c r="R56" t="n">
-        <v>6820377</v>
+        <v>6820345</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6240,7 +6245,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6250,7 +6255,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6277,7 +6282,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129129027</v>
+        <v>129129030</v>
       </c>
       <c r="B57" t="n">
         <v>79039</v>
@@ -6306,21 +6311,16 @@
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>446038</v>
+        <v>446128</v>
       </c>
       <c r="R57" t="n">
-        <v>6820345</v>
+        <v>6820377</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6362,7 +6362,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD57" t="b">

--- a/artfynd/A 37730-2023 artfynd.xlsx
+++ b/artfynd/A 37730-2023 artfynd.xlsx
@@ -4303,7 +4303,7 @@
         <v>129129057</v>
       </c>
       <c r="B39" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4410,7 +4410,7 @@
         <v>129128711</v>
       </c>
       <c r="B40" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4526,7 +4526,7 @@
         <v>129128615</v>
       </c>
       <c r="B41" t="n">
-        <v>79071</v>
+        <v>79073</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4633,7 +4633,7 @@
         <v>129128718</v>
       </c>
       <c r="B42" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         <v>129128729</v>
       </c>
       <c r="B43" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4865,7 +4865,7 @@
         <v>129128606</v>
       </c>
       <c r="B44" t="n">
-        <v>83005</v>
+        <v>83007</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         <v>129129028</v>
       </c>
       <c r="B45" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
         <v>129128684</v>
       </c>
       <c r="B46" t="n">
-        <v>80180</v>
+        <v>80182</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5191,7 +5191,7 @@
         <v>129129069</v>
       </c>
       <c r="B47" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
         <v>129128609</v>
       </c>
       <c r="B48" t="n">
-        <v>79071</v>
+        <v>79073</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5410,7 +5410,7 @@
         <v>129128710</v>
       </c>
       <c r="B49" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5526,7 +5526,7 @@
         <v>129129042</v>
       </c>
       <c r="B50" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5633,7 +5633,7 @@
         <v>129129026</v>
       </c>
       <c r="B51" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5852,7 +5852,7 @@
         <v>129129029</v>
       </c>
       <c r="B53" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5956,32 +5956,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129129056</v>
+        <v>129128639</v>
       </c>
       <c r="B54" t="n">
-        <v>92833</v>
+        <v>57724</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5991,7 +5991,7 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>446126</v>
+        <v>446125</v>
       </c>
       <c r="R54" t="n">
         <v>6820377</v>
@@ -6063,32 +6063,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129128639</v>
+        <v>129129056</v>
       </c>
       <c r="B55" t="n">
-        <v>57722</v>
+        <v>92835</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6098,7 +6098,7 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>446125</v>
+        <v>446126</v>
       </c>
       <c r="R55" t="n">
         <v>6820377</v>
@@ -6173,7 +6173,7 @@
         <v>129129027</v>
       </c>
       <c r="B56" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6285,7 +6285,7 @@
         <v>129129030</v>
       </c>
       <c r="B57" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 37730-2023 artfynd.xlsx
+++ b/artfynd/A 37730-2023 artfynd.xlsx
@@ -4523,45 +4523,54 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129128615</v>
+        <v>129128718</v>
       </c>
       <c r="B41" t="n">
-        <v>79073</v>
+        <v>98678</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>446133</v>
+        <v>446097</v>
       </c>
       <c r="R41" t="n">
-        <v>6820337</v>
+        <v>6820373</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4593,7 +4602,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4603,7 +4612,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4630,7 +4639,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129128718</v>
+        <v>129128729</v>
       </c>
       <c r="B42" t="n">
         <v>98678</v>
@@ -4660,7 +4669,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4674,10 +4683,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>446097</v>
+        <v>446069</v>
       </c>
       <c r="R42" t="n">
-        <v>6820373</v>
+        <v>6820383</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4709,7 +4718,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -4719,7 +4728,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4746,54 +4755,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129128729</v>
+        <v>129128615</v>
       </c>
       <c r="B43" t="n">
-        <v>98678</v>
+        <v>79073</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>446069</v>
+        <v>446133</v>
       </c>
       <c r="R43" t="n">
-        <v>6820383</v>
+        <v>6820337</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4825,7 +4825,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -4835,7 +4835,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4862,10 +4862,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129128606</v>
+        <v>129129028</v>
       </c>
       <c r="B44" t="n">
-        <v>83007</v>
+        <v>79041</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4873,34 +4873,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>446023</v>
+        <v>446053</v>
       </c>
       <c r="R44" t="n">
-        <v>6820366</v>
+        <v>6820359</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4932,7 +4937,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -4942,7 +4947,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4969,10 +4974,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129129028</v>
+        <v>129128606</v>
       </c>
       <c r="B45" t="n">
-        <v>79041</v>
+        <v>83007</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4980,39 +4985,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>446053</v>
+        <v>446023</v>
       </c>
       <c r="R45" t="n">
-        <v>6820359</v>
+        <v>6820366</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5044,7 +5044,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5407,54 +5407,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129128710</v>
+        <v>129129042</v>
       </c>
       <c r="B49" t="n">
-        <v>98678</v>
+        <v>79041</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>446091</v>
+        <v>446133</v>
       </c>
       <c r="R49" t="n">
-        <v>6820378</v>
+        <v>6820336</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5486,7 +5477,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5496,7 +5487,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5523,45 +5514,54 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129129042</v>
+        <v>129128710</v>
       </c>
       <c r="B50" t="n">
-        <v>79041</v>
+        <v>98678</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>446133</v>
+        <v>446091</v>
       </c>
       <c r="R50" t="n">
-        <v>6820336</v>
+        <v>6820378</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5593,7 +5593,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5603,7 +5603,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5956,32 +5956,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129128639</v>
+        <v>129129056</v>
       </c>
       <c r="B54" t="n">
-        <v>57724</v>
+        <v>92835</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5991,7 +5991,7 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>446125</v>
+        <v>446126</v>
       </c>
       <c r="R54" t="n">
         <v>6820377</v>
@@ -6063,32 +6063,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129129056</v>
+        <v>129128639</v>
       </c>
       <c r="B55" t="n">
-        <v>92835</v>
+        <v>57724</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6098,7 +6098,7 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>446126</v>
+        <v>446125</v>
       </c>
       <c r="R55" t="n">
         <v>6820377</v>

--- a/artfynd/A 37730-2023 artfynd.xlsx
+++ b/artfynd/A 37730-2023 artfynd.xlsx
@@ -4303,7 +4303,7 @@
         <v>129129057</v>
       </c>
       <c r="B39" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4410,7 +4410,7 @@
         <v>129128711</v>
       </c>
       <c r="B40" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4523,54 +4523,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129128718</v>
+        <v>129128615</v>
       </c>
       <c r="B41" t="n">
-        <v>98678</v>
+        <v>79073</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>446097</v>
+        <v>446133</v>
       </c>
       <c r="R41" t="n">
-        <v>6820373</v>
+        <v>6820337</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4602,7 +4593,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4612,7 +4603,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4639,10 +4630,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129128729</v>
+        <v>129128718</v>
       </c>
       <c r="B42" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4669,7 +4660,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4683,10 +4674,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>446069</v>
+        <v>446097</v>
       </c>
       <c r="R42" t="n">
-        <v>6820383</v>
+        <v>6820373</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4718,7 +4709,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -4728,7 +4719,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4755,45 +4746,54 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129128615</v>
+        <v>129128729</v>
       </c>
       <c r="B43" t="n">
-        <v>79073</v>
+        <v>98704</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>446133</v>
+        <v>446069</v>
       </c>
       <c r="R43" t="n">
-        <v>6820337</v>
+        <v>6820383</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4825,7 +4825,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -4835,7 +4835,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4862,10 +4862,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129129028</v>
+        <v>129128606</v>
       </c>
       <c r="B44" t="n">
-        <v>79041</v>
+        <v>83007</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4873,39 +4873,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>446053</v>
+        <v>446023</v>
       </c>
       <c r="R44" t="n">
-        <v>6820359</v>
+        <v>6820366</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4937,7 +4932,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -4947,7 +4942,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4974,10 +4969,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129128606</v>
+        <v>129129028</v>
       </c>
       <c r="B45" t="n">
-        <v>83007</v>
+        <v>79041</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4985,34 +4980,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>446023</v>
+        <v>446053</v>
       </c>
       <c r="R45" t="n">
-        <v>6820366</v>
+        <v>6820359</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5044,7 +5044,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5517,7 +5517,7 @@
         <v>129128710</v>
       </c>
       <c r="B50" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5959,7 +5959,7 @@
         <v>129129056</v>
       </c>
       <c r="B54" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 37730-2023 artfynd.xlsx
+++ b/artfynd/A 37730-2023 artfynd.xlsx
@@ -4303,7 +4303,7 @@
         <v>129129057</v>
       </c>
       <c r="B39" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4410,7 +4410,7 @@
         <v>129128711</v>
       </c>
       <c r="B40" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4630,10 +4630,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129128718</v>
+        <v>129128729</v>
       </c>
       <c r="B42" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4674,10 +4674,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>446097</v>
+        <v>446069</v>
       </c>
       <c r="R42" t="n">
-        <v>6820373</v>
+        <v>6820383</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4709,7 +4709,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4746,10 +4746,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129128729</v>
+        <v>129128718</v>
       </c>
       <c r="B43" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -4790,10 +4790,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>446069</v>
+        <v>446097</v>
       </c>
       <c r="R43" t="n">
-        <v>6820383</v>
+        <v>6820373</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4825,7 +4825,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -4835,7 +4835,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5407,45 +5407,54 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129129042</v>
+        <v>129128710</v>
       </c>
       <c r="B49" t="n">
-        <v>79041</v>
+        <v>98705</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>446133</v>
+        <v>446091</v>
       </c>
       <c r="R49" t="n">
-        <v>6820336</v>
+        <v>6820378</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5477,7 +5486,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5487,7 +5496,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5514,54 +5523,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129128710</v>
+        <v>129129042</v>
       </c>
       <c r="B50" t="n">
-        <v>98704</v>
+        <v>79041</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>446091</v>
+        <v>446133</v>
       </c>
       <c r="R50" t="n">
-        <v>6820378</v>
+        <v>6820336</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5593,7 +5593,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5603,7 +5603,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5959,7 +5959,7 @@
         <v>129129056</v>
       </c>
       <c r="B54" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 37730-2023 artfynd.xlsx
+++ b/artfynd/A 37730-2023 artfynd.xlsx
@@ -4410,7 +4410,7 @@
         <v>129128711</v>
       </c>
       <c r="B40" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4630,10 +4630,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129128729</v>
+        <v>129128718</v>
       </c>
       <c r="B42" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4674,10 +4674,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>446069</v>
+        <v>446097</v>
       </c>
       <c r="R42" t="n">
-        <v>6820383</v>
+        <v>6820373</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4709,7 +4709,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4746,10 +4746,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129128718</v>
+        <v>129128729</v>
       </c>
       <c r="B43" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -4790,10 +4790,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>446097</v>
+        <v>446069</v>
       </c>
       <c r="R43" t="n">
-        <v>6820373</v>
+        <v>6820383</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4825,7 +4825,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -4835,7 +4835,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5407,54 +5407,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129128710</v>
+        <v>129129042</v>
       </c>
       <c r="B49" t="n">
-        <v>98705</v>
+        <v>79041</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>446091</v>
+        <v>446133</v>
       </c>
       <c r="R49" t="n">
-        <v>6820378</v>
+        <v>6820336</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5486,7 +5477,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5496,7 +5487,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5523,45 +5514,54 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129129042</v>
+        <v>129128710</v>
       </c>
       <c r="B50" t="n">
-        <v>79041</v>
+        <v>98706</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Balser, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>446133</v>
+        <v>446091</v>
       </c>
       <c r="R50" t="n">
-        <v>6820336</v>
+        <v>6820378</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5593,7 +5593,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5603,7 +5603,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5956,32 +5956,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129129056</v>
+        <v>129128639</v>
       </c>
       <c r="B54" t="n">
-        <v>92822</v>
+        <v>57724</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5991,7 +5991,7 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>446126</v>
+        <v>446125</v>
       </c>
       <c r="R54" t="n">
         <v>6820377</v>
@@ -6063,32 +6063,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129128639</v>
+        <v>129129056</v>
       </c>
       <c r="B55" t="n">
-        <v>57724</v>
+        <v>92822</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6098,7 +6098,7 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>446125</v>
+        <v>446126</v>
       </c>
       <c r="R55" t="n">
         <v>6820377</v>

--- a/artfynd/A 37730-2023 artfynd.xlsx
+++ b/artfynd/A 37730-2023 artfynd.xlsx
@@ -4303,7 +4303,7 @@
         <v>129129057</v>
       </c>
       <c r="B39" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4410,7 +4410,7 @@
         <v>129128711</v>
       </c>
       <c r="B40" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4526,7 +4526,7 @@
         <v>129128615</v>
       </c>
       <c r="B41" t="n">
-        <v>79073</v>
+        <v>79075</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4633,7 +4633,7 @@
         <v>129128718</v>
       </c>
       <c r="B42" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         <v>129128729</v>
       </c>
       <c r="B43" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4865,7 +4865,7 @@
         <v>129128606</v>
       </c>
       <c r="B44" t="n">
-        <v>83007</v>
+        <v>83011</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         <v>129129028</v>
       </c>
       <c r="B45" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
         <v>129128684</v>
       </c>
       <c r="B46" t="n">
-        <v>80182</v>
+        <v>80184</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
         <v>129128609</v>
       </c>
       <c r="B48" t="n">
-        <v>79073</v>
+        <v>79075</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5410,7 +5410,7 @@
         <v>129129042</v>
       </c>
       <c r="B49" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5517,7 +5517,7 @@
         <v>129128710</v>
       </c>
       <c r="B50" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5633,7 +5633,7 @@
         <v>129129026</v>
       </c>
       <c r="B51" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5852,7 +5852,7 @@
         <v>129129029</v>
       </c>
       <c r="B53" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5956,32 +5956,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129128639</v>
+        <v>129129056</v>
       </c>
       <c r="B54" t="n">
-        <v>57724</v>
+        <v>92825</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5991,7 +5991,7 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>446125</v>
+        <v>446126</v>
       </c>
       <c r="R54" t="n">
         <v>6820377</v>
@@ -6063,32 +6063,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129129056</v>
+        <v>129128639</v>
       </c>
       <c r="B55" t="n">
-        <v>92822</v>
+        <v>57724</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6098,7 +6098,7 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>446126</v>
+        <v>446125</v>
       </c>
       <c r="R55" t="n">
         <v>6820377</v>
@@ -6173,7 +6173,7 @@
         <v>129129027</v>
       </c>
       <c r="B56" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6285,7 +6285,7 @@
         <v>129129030</v>
       </c>
       <c r="B57" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 37730-2023 artfynd.xlsx
+++ b/artfynd/A 37730-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY64"/>
+  <dimension ref="A1:AZ64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129128609</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129128612</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129128613</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129128615</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129129056</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129129057</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1411,6 +1446,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128601876</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1508,6 +1548,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128601877</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1605,6 +1650,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128601879</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1702,6 +1752,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128601880</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1799,6 +1854,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128601881</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1896,6 +1956,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128601882</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1993,6 +2058,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128601883</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2090,6 +2160,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128601891</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2187,6 +2262,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128601896</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2284,6 +2364,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128601897</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2381,6 +2466,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128601899</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2478,6 +2568,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128601900</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2575,6 +2670,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128601901</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2672,6 +2772,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128601902</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2769,6 +2874,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128601903</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2866,6 +2976,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128601904</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2963,6 +3078,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128601905</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3060,6 +3180,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128601906</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3157,6 +3282,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128601907</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3254,6 +3384,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128601908</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3351,6 +3486,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128601909</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3448,6 +3588,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128601910</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3545,6 +3690,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128601911</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3642,6 +3792,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128601912</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3739,6 +3894,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128601913</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3836,6 +3996,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128601914</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3933,6 +4098,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128601915</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4030,6 +4200,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128601916</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4127,6 +4302,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128601917</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4224,6 +4404,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128601918</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4321,6 +4506,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128601919</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4428,6 +4618,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129129026</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4540,6 +4735,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129129027</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4652,6 +4852,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129129028</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4759,6 +4964,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129129029</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4866,6 +5076,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129129030</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4973,6 +5188,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129129041</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5080,6 +5300,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129129042</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5187,6 +5412,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129128606</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5294,6 +5524,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129128684</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5399,6 +5634,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128601862</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5504,6 +5744,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128601863</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5601,6 +5846,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128601864</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5706,6 +5956,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128601865</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5811,6 +6066,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128601866</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5918,6 +6178,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129128639</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6030,6 +6295,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129129069</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6142,6 +6412,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129129068</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6258,6 +6533,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129128710</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6374,6 +6654,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129128711</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6490,6 +6775,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129128718</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6606,6 +6896,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129128729</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6703,6 +6998,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128601869</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6800,6 +7100,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128601870</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6897,6 +7202,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128601871</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6994,6 +7304,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128601873</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7095,8 +7410,78 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128601921</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>